--- a/reports/MyPortfolio_Tracker_Kenya_Dashboard_Output.xlsx
+++ b/reports/MyPortfolio_Tracker_Kenya_Dashboard_Output.xlsx
@@ -820,7 +820,7 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>25954263.69</v>
+        <v>26192713.69</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
@@ -869,10 +869,10 @@
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>1059300</v>
+        <v>1056000</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>4.081410332623465</v>
+        <v>4.03165556840781</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -882,10 +882,10 @@
         </is>
       </c>
       <c r="B11" s="10" t="n">
-        <v>1113750</v>
+        <v>1128750</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>4.29120245252467</v>
+        <v>4.309404567083633</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -898,7 +898,7 @@
         <v>1299375</v>
       </c>
       <c r="C12" s="8" t="n">
-        <v>5.006402861278782</v>
+        <v>4.960826187689298</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -908,10 +908,10 @@
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>1277340</v>
+        <v>1288320</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>4.921503515787083</v>
+        <v>4.91861979345753</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -921,10 +921,10 @@
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>2452706.75</v>
+        <v>2488835</v>
       </c>
       <c r="C14" s="8" t="n">
-        <v>9.450111085004547</v>
+        <v>9.50201277139986</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="B15" s="10" t="n">
-        <v>1698120</v>
+        <v>1826658.25</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>6.542740030241251</v>
+        <v>6.973917523854703</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -950,7 +950,7 @@
         <v>819547.2400000001</v>
       </c>
       <c r="C16" s="8" t="n">
-        <v>3.157659372613087</v>
+        <v>3.128913062234141</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -960,10 +960,10 @@
         </is>
       </c>
       <c r="B17" s="10" t="n">
-        <v>744211.5</v>
+        <v>756312.5</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>2.867395927270091</v>
+        <v>2.887491952728629</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -973,10 +973,10 @@
         </is>
       </c>
       <c r="B18" s="7" t="n">
-        <v>909263.9999999999</v>
+        <v>907270</v>
       </c>
       <c r="C18" s="8" t="n">
-        <v>3.503331902843898</v>
+        <v>3.463825897300525</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -986,10 +986,10 @@
         </is>
       </c>
       <c r="B19" s="10" t="n">
-        <v>1464784.2</v>
+        <v>1473967.8</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>5.643713177516847</v>
+        <v>5.627396295950578</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -999,10 +999,10 @@
         </is>
       </c>
       <c r="B20" s="7" t="n">
-        <v>1393708</v>
+        <v>1425520.9</v>
       </c>
       <c r="C20" s="8" t="n">
-        <v>5.369861447993943</v>
+        <v>5.442433024968478</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -1015,7 +1015,7 @@
         <v>2559858</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>9.862957510855127</v>
+        <v>9.77316833336485</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -1028,7 +1028,7 @@
         <v>1112299</v>
       </c>
       <c r="C22" s="8" t="n">
-        <v>4.285611848925467</v>
+        <v>4.246597023754204</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -1041,7 +1041,7 @@
         <v>6050000</v>
       </c>
       <c r="C23" s="11" t="n">
-        <v>23.31023554457846</v>
+        <v>23.09802669400308</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -1054,7 +1054,7 @@
         <v>2000000</v>
       </c>
       <c r="C24" s="8" t="n">
-        <v>7.705862989943292</v>
+        <v>7.635711303802671</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1"/>
@@ -1078,7 +1078,7 @@
         </is>
       </c>
       <c r="B28" s="8" t="n">
-        <v>18.300519162214</v>
+        <v>18.22050611663827</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -1088,7 +1088,7 @@
         </is>
       </c>
       <c r="B29" s="11" t="n">
-        <v>7.705862989943292</v>
+        <v>7.635711303802671</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -1098,7 +1098,7 @@
         </is>
       </c>
       <c r="B30" s="8" t="n">
-        <v>14.14856935978059</v>
+        <v>14.01976535711905</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -1108,7 +1108,7 @@
         </is>
       </c>
       <c r="B31" s="11" t="n">
-        <v>14.51690652835469</v>
+        <v>14.53365521821958</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="B32" s="8" t="n">
-        <v>23.31023554457846</v>
+        <v>23.09802669400308</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B33" s="11" t="n">
-        <v>12.56779533012443</v>
+        <v>12.99032253881747</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -1138,7 +1138,7 @@
         </is>
       </c>
       <c r="B34" s="8" t="n">
-        <v>9.450111085004547</v>
+        <v>9.50201277139986</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1"/>
@@ -1267,22 +1267,22 @@
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>KCB</t>
+          <t>Jubilee</t>
         </is>
       </c>
       <c r="B48" s="12" t="inlineStr">
         <is>
-          <t>Banking</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="C48" s="8" t="n">
-        <v>5.006402861278782</v>
+        <v>6.973917523854703</v>
       </c>
       <c r="D48" s="8" t="n">
-        <v>5</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="E48" s="8" t="n">
-        <v>0.00640286127878209</v>
+        <v>0.3072508571880359</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1"/>
@@ -1330,22 +1330,22 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>KCB</t>
+          <t>Jubilee</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>Banking</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="D54" s="3" t="n">
-        <v>25</v>
+        <v>208</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>68.75</v>
+        <v>387.25</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>1718.75</v>
+        <v>80548</v>
       </c>
       <c r="G54" s="15" t="inlineStr">
         <is>
@@ -1370,13 +1370,13 @@
         </is>
       </c>
       <c r="D55" s="16" t="n">
-        <v>136</v>
+        <v>6439</v>
       </c>
       <c r="E55" s="10" t="n">
-        <v>12.3</v>
+        <v>12.5</v>
       </c>
       <c r="F55" s="10" t="n">
-        <v>1672.8</v>
+        <v>80487.5</v>
       </c>
       <c r="G55" s="17" t="inlineStr">
         <is>
@@ -1528,13 +1528,13 @@
         <v>32.1</v>
       </c>
       <c r="G2" s="23" t="n">
-        <v>32.1</v>
+        <v>32</v>
       </c>
       <c r="H2" s="19" t="n">
         <v>1059300</v>
       </c>
       <c r="I2" s="23" t="n">
-        <v>1059300</v>
+        <v>1056000</v>
       </c>
       <c r="J2" s="23" t="n">
         <v>66000</v>
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="L2" s="19" t="n">
-        <v>32.1</v>
+        <v>32</v>
       </c>
       <c r="M2" s="19" t="inlineStr">
         <is>
@@ -1554,14 +1554,14 @@
       </c>
       <c r="N2" s="19" t="inlineStr">
         <is>
-          <t>2026-06-01 16:27:07</t>
+          <t>2026-06-02 21:41:29</t>
         </is>
       </c>
       <c r="O2" s="24" t="n">
-        <v>4.081410332623465</v>
+        <v>4.03165556840781</v>
       </c>
       <c r="P2" s="24" t="n">
-        <v>0</v>
+        <v>-0.3115264797507832</v>
       </c>
     </row>
     <row r="3">
@@ -1588,13 +1588,13 @@
         <v>74.25</v>
       </c>
       <c r="G3" s="27" t="n">
-        <v>74.25</v>
+        <v>75.25</v>
       </c>
       <c r="H3" s="17" t="n">
         <v>1113750</v>
       </c>
       <c r="I3" s="27" t="n">
-        <v>1113750</v>
+        <v>1128750</v>
       </c>
       <c r="J3" s="27" t="n">
         <v>30000</v>
@@ -1605,7 +1605,7 @@
         </is>
       </c>
       <c r="L3" s="17" t="n">
-        <v>74.25</v>
+        <v>75.25</v>
       </c>
       <c r="M3" s="17" t="inlineStr">
         <is>
@@ -1614,14 +1614,14 @@
       </c>
       <c r="N3" s="17" t="inlineStr">
         <is>
-          <t>2026-06-01 16:27:07</t>
+          <t>2026-06-02 21:41:29</t>
         </is>
       </c>
       <c r="O3" s="28" t="n">
-        <v>4.29120245252467</v>
+        <v>4.309404567083633</v>
       </c>
       <c r="P3" s="28" t="n">
-        <v>0</v>
+        <v>1.346801346801347</v>
       </c>
     </row>
     <row r="4">
@@ -1672,11 +1672,11 @@
       </c>
       <c r="N4" s="19" t="inlineStr">
         <is>
-          <t>2026-06-01 16:27:07</t>
+          <t>2026-06-02 21:41:29</t>
         </is>
       </c>
       <c r="O4" s="24" t="n">
-        <v>5.006402861278782</v>
+        <v>4.960826187689298</v>
       </c>
       <c r="P4" s="24" t="n">
         <v>2.99625468164794</v>
@@ -1706,13 +1706,13 @@
         <v>87.25</v>
       </c>
       <c r="G5" s="27" t="n">
-        <v>87.25</v>
+        <v>88</v>
       </c>
       <c r="H5" s="17" t="n">
         <v>1277340</v>
       </c>
       <c r="I5" s="27" t="n">
-        <v>1277340</v>
+        <v>1288320</v>
       </c>
       <c r="J5" s="27" t="n">
         <v>29280</v>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="L5" s="17" t="n">
-        <v>87.25</v>
+        <v>88</v>
       </c>
       <c r="M5" s="17" t="inlineStr">
         <is>
@@ -1732,14 +1732,14 @@
       </c>
       <c r="N5" s="17" t="inlineStr">
         <is>
-          <t>2026-06-01 16:27:07</t>
+          <t>2026-06-02 21:41:29</t>
         </is>
       </c>
       <c r="O5" s="28" t="n">
-        <v>4.921503515787083</v>
+        <v>4.91861979345753</v>
       </c>
       <c r="P5" s="28" t="n">
-        <v>0</v>
+        <v>0.8595988538681949</v>
       </c>
     </row>
     <row r="6">
@@ -1766,13 +1766,13 @@
         <v>30.55</v>
       </c>
       <c r="G6" s="23" t="n">
-        <v>30.55</v>
+        <v>31</v>
       </c>
       <c r="H6" s="19" t="n">
         <v>2452706.75</v>
       </c>
       <c r="I6" s="23" t="n">
-        <v>2452706.75</v>
+        <v>2488835</v>
       </c>
       <c r="J6" s="23" t="n">
         <v>160570</v>
@@ -1783,7 +1783,7 @@
         </is>
       </c>
       <c r="L6" s="19" t="n">
-        <v>30.55</v>
+        <v>31</v>
       </c>
       <c r="M6" s="19" t="inlineStr">
         <is>
@@ -1792,14 +1792,14 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>2026-06-01 16:27:07</t>
+          <t>2026-06-02 21:41:29</t>
         </is>
       </c>
       <c r="O6" s="24" t="n">
-        <v>9.450111085004547</v>
+        <v>9.50201277139986</v>
       </c>
       <c r="P6" s="24" t="n">
-        <v>0</v>
+        <v>1.472995090016364</v>
       </c>
     </row>
     <row r="7">
@@ -1826,13 +1826,13 @@
         <v>360</v>
       </c>
       <c r="G7" s="27" t="n">
-        <v>360</v>
+        <v>387.25</v>
       </c>
       <c r="H7" s="17" t="n">
         <v>1698120</v>
       </c>
       <c r="I7" s="27" t="n">
-        <v>1698120</v>
+        <v>1826658.25</v>
       </c>
       <c r="J7" s="27" t="n">
         <v>9434</v>
@@ -1843,7 +1843,7 @@
         </is>
       </c>
       <c r="L7" s="17" t="n">
-        <v>360</v>
+        <v>387.25</v>
       </c>
       <c r="M7" s="17" t="inlineStr">
         <is>
@@ -1852,14 +1852,14 @@
       </c>
       <c r="N7" s="17" t="inlineStr">
         <is>
-          <t>2026-06-01 16:27:07</t>
+          <t>2026-06-02 21:41:29</t>
         </is>
       </c>
       <c r="O7" s="28" t="n">
-        <v>6.542740030241251</v>
+        <v>6.973917523854703</v>
       </c>
       <c r="P7" s="28" t="n">
-        <v>0</v>
+        <v>7.569444444444444</v>
       </c>
     </row>
     <row r="8">
@@ -1912,11 +1912,11 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>2026-06-01 16:27:07</t>
+          <t>2026-06-02 21:41:29</t>
         </is>
       </c>
       <c r="O8" s="24" t="n">
-        <v>3.157659372613087</v>
+        <v>3.128913062234141</v>
       </c>
       <c r="P8" s="24" t="n">
         <v>0</v>
@@ -1946,13 +1946,13 @@
         <v>12.85</v>
       </c>
       <c r="G9" s="27" t="n">
-        <v>12.3</v>
+        <v>12.5</v>
       </c>
       <c r="H9" s="17" t="n">
         <v>777489.25</v>
       </c>
       <c r="I9" s="27" t="n">
-        <v>744211.5</v>
+        <v>756312.5</v>
       </c>
       <c r="J9" s="27" t="n">
         <v>121010</v>
@@ -1963,7 +1963,7 @@
         </is>
       </c>
       <c r="L9" s="17" t="n">
-        <v>12.3</v>
+        <v>12.5</v>
       </c>
       <c r="M9" s="17" t="inlineStr">
         <is>
@@ -1972,14 +1972,14 @@
       </c>
       <c r="N9" s="17" t="inlineStr">
         <is>
-          <t>2026-06-01 16:27:07</t>
+          <t>2026-06-02 21:41:29</t>
         </is>
       </c>
       <c r="O9" s="28" t="n">
-        <v>2.867395927270091</v>
+        <v>2.887491952728629</v>
       </c>
       <c r="P9" s="28" t="n">
-        <v>-4.280155642023338</v>
+        <v>-2.723735408560309</v>
       </c>
     </row>
     <row r="10">
@@ -2006,13 +2006,13 @@
         <v>9.18</v>
       </c>
       <c r="G10" s="23" t="n">
-        <v>9.119999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="H10" s="19" t="n">
         <v>915246</v>
       </c>
       <c r="I10" s="23" t="n">
-        <v>909263.9999999999</v>
+        <v>907270</v>
       </c>
       <c r="J10" s="23" t="n">
         <v>199400</v>
@@ -2023,7 +2023,7 @@
         </is>
       </c>
       <c r="L10" s="19" t="n">
-        <v>9.119999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="M10" s="19" t="inlineStr">
         <is>
@@ -2032,14 +2032,14 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>2026-06-01 16:27:07</t>
+          <t>2026-06-02 21:41:29</t>
         </is>
       </c>
       <c r="O10" s="24" t="n">
-        <v>3.503331902843898</v>
+        <v>3.463825897300525</v>
       </c>
       <c r="P10" s="24" t="n">
-        <v>-0.6535947712418355</v>
+        <v>-0.8714596949891076</v>
       </c>
     </row>
     <row r="11">
@@ -2066,13 +2066,13 @@
         <v>15.35</v>
       </c>
       <c r="G11" s="27" t="n">
-        <v>15.95</v>
+        <v>16.05</v>
       </c>
       <c r="H11" s="17" t="n">
         <v>1409682.6</v>
       </c>
       <c r="I11" s="27" t="n">
-        <v>1464784.2</v>
+        <v>1473967.8</v>
       </c>
       <c r="J11" s="27" t="n">
         <v>183672.0000000002</v>
@@ -2083,7 +2083,7 @@
         </is>
       </c>
       <c r="L11" s="17" t="n">
-        <v>15.95</v>
+        <v>16.05</v>
       </c>
       <c r="M11" s="17" t="inlineStr">
         <is>
@@ -2092,14 +2092,14 @@
       </c>
       <c r="N11" s="17" t="inlineStr">
         <is>
-          <t>2026-06-01 16:27:07</t>
+          <t>2026-06-02 21:41:29</t>
         </is>
       </c>
       <c r="O11" s="28" t="n">
-        <v>5.643713177516847</v>
+        <v>5.627396295950578</v>
       </c>
       <c r="P11" s="28" t="n">
-        <v>3.908794788273613</v>
+        <v>4.560260586319225</v>
       </c>
     </row>
     <row r="12">
@@ -2126,13 +2126,13 @@
         <v>55.5</v>
       </c>
       <c r="G12" s="23" t="n">
-        <v>46</v>
+        <v>47.05</v>
       </c>
       <c r="H12" s="19" t="n">
         <v>1681539</v>
       </c>
       <c r="I12" s="23" t="n">
-        <v>1393708</v>
+        <v>1425520.9</v>
       </c>
       <c r="J12" s="23" t="n">
         <v>60596</v>
@@ -2143,7 +2143,7 @@
         </is>
       </c>
       <c r="L12" s="19" t="n">
-        <v>46</v>
+        <v>47.05</v>
       </c>
       <c r="M12" s="19" t="inlineStr">
         <is>
@@ -2152,14 +2152,14 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>2026-06-01 16:27:07</t>
+          <t>2026-06-02 21:41:29</t>
         </is>
       </c>
       <c r="O12" s="24" t="n">
-        <v>5.369861447993943</v>
+        <v>5.442433024968478</v>
       </c>
       <c r="P12" s="24" t="n">
-        <v>-17.11711711711712</v>
+        <v>-15.22522522522523</v>
       </c>
     </row>
     <row r="13">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="N13" s="17" t="inlineStr"/>
       <c r="O13" s="28" t="n">
-        <v>9.862957510855127</v>
+        <v>9.77316833336485</v>
       </c>
       <c r="P13" s="28" t="n">
         <v>0.003828483920367535</v>
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr"/>
       <c r="O14" s="24" t="n">
-        <v>4.285611848925467</v>
+        <v>4.246597023754204</v>
       </c>
       <c r="P14" s="24" t="n">
         <v>0.01744439598778892</v>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="N15" s="17" t="inlineStr"/>
       <c r="O15" s="28" t="n">
-        <v>23.31023554457846</v>
+        <v>23.09802669400308</v>
       </c>
       <c r="P15" s="28" t="n">
         <v>0</v>
@@ -2356,7 +2356,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr"/>
       <c r="O16" s="24" t="n">
-        <v>7.705862989943292</v>
+        <v>7.635711303802671</v>
       </c>
       <c r="P16" s="24" t="n">
         <v>0</v>
@@ -2443,7 +2443,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="23" t="n">
-        <v>1059300</v>
+        <v>1056000</v>
       </c>
       <c r="H2" s="19" t="n">
         <v>0</v>
@@ -2465,7 +2465,7 @@
         <v>0</v>
       </c>
       <c r="G3" s="27" t="n">
-        <v>1113750</v>
+        <v>1128750</v>
       </c>
       <c r="H3" s="17" t="n">
         <v>0</v>
@@ -2509,7 +2509,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="27" t="n">
-        <v>1277340</v>
+        <v>1288320</v>
       </c>
       <c r="H5" s="17" t="n">
         <v>0</v>
@@ -2531,7 +2531,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="23" t="n">
-        <v>2452706.75</v>
+        <v>2488835</v>
       </c>
       <c r="H6" s="19" t="n">
         <v>0</v>
@@ -2553,7 +2553,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="27" t="n">
-        <v>1698120</v>
+        <v>1826658.25</v>
       </c>
       <c r="H7" s="17" t="n">
         <v>0</v>
@@ -2597,7 +2597,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="27" t="n">
-        <v>744211.5</v>
+        <v>756312.5</v>
       </c>
       <c r="H9" s="17" t="n">
         <v>0</v>
@@ -2619,7 +2619,7 @@
         <v>0</v>
       </c>
       <c r="G10" s="23" t="n">
-        <v>909263.9999999999</v>
+        <v>907270</v>
       </c>
       <c r="H10" s="19" t="n">
         <v>0</v>
@@ -2661,7 +2661,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="23" t="n">
-        <v>1393708</v>
+        <v>1425520.9</v>
       </c>
       <c r="H12" s="19" t="n">
         <v>0</v>
@@ -2826,11 +2826,11 @@
     <row r="2">
       <c r="A2" s="21" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>25954263.69</v>
+        <v>26192713.69</v>
       </c>
       <c r="C2" s="23" t="inlineStr">
         <is>
@@ -3029,7 +3029,7 @@
         </is>
       </c>
       <c r="C2" s="23" t="n">
-        <v>32.1</v>
+        <v>32</v>
       </c>
       <c r="D2" s="19" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
       </c>
       <c r="E2" s="19" t="inlineStr">
         <is>
-          <t>2026-06-01 16:27:07</t>
+          <t>2026-06-02 21:41:29</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
         </is>
       </c>
       <c r="C3" s="27" t="n">
-        <v>74.25</v>
+        <v>75.25</v>
       </c>
       <c r="D3" s="17" t="inlineStr">
         <is>
@@ -3063,7 +3063,7 @@
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>2026-06-01 16:27:07</t>
+          <t>2026-06-02 21:41:29</t>
         </is>
       </c>
     </row>
@@ -3088,7 +3088,7 @@
       </c>
       <c r="E4" s="19" t="inlineStr">
         <is>
-          <t>2026-06-01 16:27:07</t>
+          <t>2026-06-02 21:41:29</t>
         </is>
       </c>
     </row>
@@ -3104,7 +3104,7 @@
         </is>
       </c>
       <c r="C5" s="27" t="n">
-        <v>87.25</v>
+        <v>88</v>
       </c>
       <c r="D5" s="17" t="inlineStr">
         <is>
@@ -3113,7 +3113,7 @@
       </c>
       <c r="E5" s="17" t="inlineStr">
         <is>
-          <t>2026-06-01 16:27:07</t>
+          <t>2026-06-02 21:41:29</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="C6" s="23" t="n">
-        <v>30.55</v>
+        <v>31</v>
       </c>
       <c r="D6" s="19" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="E6" s="19" t="inlineStr">
         <is>
-          <t>2026-06-01 16:27:07</t>
+          <t>2026-06-02 21:41:29</t>
         </is>
       </c>
     </row>
@@ -3154,7 +3154,7 @@
         </is>
       </c>
       <c r="C7" s="27" t="n">
-        <v>360</v>
+        <v>387.25</v>
       </c>
       <c r="D7" s="17" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
       </c>
       <c r="E7" s="17" t="inlineStr">
         <is>
-          <t>2026-06-01 16:27:07</t>
+          <t>2026-06-02 21:41:29</t>
         </is>
       </c>
     </row>
@@ -3188,7 +3188,7 @@
       </c>
       <c r="E8" s="19" t="inlineStr">
         <is>
-          <t>2026-06-01 16:27:07</t>
+          <t>2026-06-02 21:41:29</t>
         </is>
       </c>
     </row>
@@ -3204,7 +3204,7 @@
         </is>
       </c>
       <c r="C9" s="27" t="n">
-        <v>12.3</v>
+        <v>12.5</v>
       </c>
       <c r="D9" s="17" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="E9" s="17" t="inlineStr">
         <is>
-          <t>2026-06-01 16:27:07</t>
+          <t>2026-06-02 21:41:29</t>
         </is>
       </c>
     </row>
@@ -3229,7 +3229,7 @@
         </is>
       </c>
       <c r="C10" s="23" t="n">
-        <v>9.119999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="D10" s="19" t="inlineStr">
         <is>
@@ -3238,7 +3238,7 @@
       </c>
       <c r="E10" s="19" t="inlineStr">
         <is>
-          <t>2026-06-01 16:27:07</t>
+          <t>2026-06-02 21:41:29</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
         </is>
       </c>
       <c r="C11" s="27" t="n">
-        <v>15.95</v>
+        <v>16.05</v>
       </c>
       <c r="D11" s="17" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="E11" s="17" t="inlineStr">
         <is>
-          <t>2026-06-01 16:27:07</t>
+          <t>2026-06-02 21:41:29</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
         </is>
       </c>
       <c r="C12" s="23" t="n">
-        <v>46</v>
+        <v>47.05</v>
       </c>
       <c r="D12" s="19" t="inlineStr">
         <is>
@@ -3288,7 +3288,7 @@
       </c>
       <c r="E12" s="19" t="inlineStr">
         <is>
-          <t>2026-06-01 16:27:07</t>
+          <t>2026-06-02 21:41:29</t>
         </is>
       </c>
     </row>
@@ -3459,7 +3459,7 @@
     <row r="2">
       <c r="A2" s="21" t="inlineStr">
         <is>
-          <t>2026-06-01 16:27:25</t>
+          <t>2026-06-02 21:42:18</t>
         </is>
       </c>
       <c r="B2" s="21" t="inlineStr">
@@ -3491,7 +3491,7 @@
         <v>0</v>
       </c>
       <c r="J2" s="23" t="n">
-        <v>0</v>
+        <v>-3300</v>
       </c>
       <c r="K2" s="23" t="n">
         <v>1059300</v>
@@ -3506,7 +3506,7 @@
     <row r="3">
       <c r="A3" s="25" t="inlineStr">
         <is>
-          <t>2026-06-01 16:27:25</t>
+          <t>2026-06-02 21:42:18</t>
         </is>
       </c>
       <c r="B3" s="25" t="inlineStr">
@@ -3538,7 +3538,7 @@
         <v>0</v>
       </c>
       <c r="J3" s="27" t="n">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="K3" s="27" t="n">
         <v>1113750</v>
@@ -3553,7 +3553,7 @@
     <row r="4">
       <c r="A4" s="21" t="inlineStr">
         <is>
-          <t>2026-06-01 16:27:25</t>
+          <t>2026-06-02 21:42:18</t>
         </is>
       </c>
       <c r="B4" s="21" t="inlineStr">
@@ -3600,7 +3600,7 @@
     <row r="5">
       <c r="A5" s="25" t="inlineStr">
         <is>
-          <t>2026-06-01 16:27:25</t>
+          <t>2026-06-02 21:42:18</t>
         </is>
       </c>
       <c r="B5" s="25" t="inlineStr">
@@ -3632,7 +3632,7 @@
         <v>0</v>
       </c>
       <c r="J5" s="27" t="n">
-        <v>0</v>
+        <v>10980</v>
       </c>
       <c r="K5" s="27" t="n">
         <v>1277340</v>
@@ -3647,7 +3647,7 @@
     <row r="6">
       <c r="A6" s="21" t="inlineStr">
         <is>
-          <t>2026-06-01 16:27:25</t>
+          <t>2026-06-02 21:42:18</t>
         </is>
       </c>
       <c r="B6" s="21" t="inlineStr">
@@ -3679,7 +3679,7 @@
         <v>0</v>
       </c>
       <c r="J6" s="23" t="n">
-        <v>0</v>
+        <v>36128.25</v>
       </c>
       <c r="K6" s="23" t="n">
         <v>2452706.75</v>
@@ -3694,7 +3694,7 @@
     <row r="7">
       <c r="A7" s="25" t="inlineStr">
         <is>
-          <t>2026-06-01 16:27:25</t>
+          <t>2026-06-02 21:42:18</t>
         </is>
       </c>
       <c r="B7" s="25" t="inlineStr">
@@ -3726,7 +3726,7 @@
         <v>0</v>
       </c>
       <c r="J7" s="27" t="n">
-        <v>0</v>
+        <v>128538.25</v>
       </c>
       <c r="K7" s="27" t="n">
         <v>1698120</v>
@@ -3741,7 +3741,7 @@
     <row r="8">
       <c r="A8" s="21" t="inlineStr">
         <is>
-          <t>2026-06-01 16:27:25</t>
+          <t>2026-06-02 21:42:18</t>
         </is>
       </c>
       <c r="B8" s="21" t="inlineStr">
@@ -3788,7 +3788,7 @@
     <row r="9">
       <c r="A9" s="25" t="inlineStr">
         <is>
-          <t>2026-06-01 16:27:25</t>
+          <t>2026-06-02 21:42:18</t>
         </is>
       </c>
       <c r="B9" s="25" t="inlineStr">
@@ -3820,7 +3820,7 @@
         <v>0</v>
       </c>
       <c r="J9" s="27" t="n">
-        <v>-33277.75</v>
+        <v>-21176.75</v>
       </c>
       <c r="K9" s="27" t="n">
         <v>777489.25</v>
@@ -3835,7 +3835,7 @@
     <row r="10">
       <c r="A10" s="21" t="inlineStr">
         <is>
-          <t>2026-06-01 16:27:25</t>
+          <t>2026-06-02 21:42:18</t>
         </is>
       </c>
       <c r="B10" s="21" t="inlineStr">
@@ -3867,7 +3867,7 @@
         <v>0</v>
       </c>
       <c r="J10" s="23" t="n">
-        <v>-5982.000000000116</v>
+        <v>-7976</v>
       </c>
       <c r="K10" s="23" t="n">
         <v>915246</v>
@@ -3882,7 +3882,7 @@
     <row r="11">
       <c r="A11" s="25" t="inlineStr">
         <is>
-          <t>2026-06-01 16:27:25</t>
+          <t>2026-06-02 21:42:18</t>
         </is>
       </c>
       <c r="B11" s="25" t="inlineStr">
@@ -3914,7 +3914,7 @@
         <v>0</v>
       </c>
       <c r="J11" s="27" t="n">
-        <v>55101.60000000009</v>
+        <v>64285.20000000019</v>
       </c>
       <c r="K11" s="27" t="n">
         <v>1409682.6</v>
@@ -3929,7 +3929,7 @@
     <row r="12">
       <c r="A12" s="21" t="inlineStr">
         <is>
-          <t>2026-06-01 16:27:25</t>
+          <t>2026-06-02 21:42:18</t>
         </is>
       </c>
       <c r="B12" s="21" t="inlineStr">
@@ -3961,7 +3961,7 @@
         <v>0</v>
       </c>
       <c r="J12" s="23" t="n">
-        <v>-287831</v>
+        <v>-256018.1000000001</v>
       </c>
       <c r="K12" s="23" t="n">
         <v>1681539</v>
@@ -3976,7 +3976,7 @@
     <row r="13">
       <c r="A13" s="25" t="inlineStr">
         <is>
-          <t>2026-06-01 16:27:25</t>
+          <t>2026-06-02 21:42:18</t>
         </is>
       </c>
       <c r="B13" s="25" t="inlineStr">
@@ -4023,7 +4023,7 @@
     <row r="14">
       <c r="A14" s="21" t="inlineStr">
         <is>
-          <t>2026-06-01 16:27:25</t>
+          <t>2026-06-02 21:42:18</t>
         </is>
       </c>
       <c r="B14" s="21" t="inlineStr">
@@ -4070,7 +4070,7 @@
     <row r="15">
       <c r="A15" s="25" t="inlineStr">
         <is>
-          <t>2026-06-01 16:27:25</t>
+          <t>2026-06-02 21:42:18</t>
         </is>
       </c>
       <c r="B15" s="25" t="inlineStr">
@@ -4117,7 +4117,7 @@
     <row r="16">
       <c r="A16" s="21" t="inlineStr">
         <is>
-          <t>2026-06-01 16:27:25</t>
+          <t>2026-06-02 21:42:18</t>
         </is>
       </c>
       <c r="B16" s="21" t="inlineStr">
@@ -4225,10 +4225,10 @@
         <v>32.1</v>
       </c>
       <c r="E2" t="n">
-        <v>32.1</v>
+        <v>32</v>
       </c>
       <c r="F2" t="n">
-        <v>1059300</v>
+        <v>1056000</v>
       </c>
     </row>
     <row r="3">
@@ -4249,10 +4249,10 @@
         <v>74.25</v>
       </c>
       <c r="E3" t="n">
-        <v>74.25</v>
+        <v>75.25</v>
       </c>
       <c r="F3" t="n">
-        <v>1113750</v>
+        <v>1128750</v>
       </c>
     </row>
     <row r="4">
@@ -4297,10 +4297,10 @@
         <v>87.25</v>
       </c>
       <c r="E5" t="n">
-        <v>87.25</v>
+        <v>88</v>
       </c>
       <c r="F5" t="n">
-        <v>1277340</v>
+        <v>1288320</v>
       </c>
     </row>
     <row r="6">
@@ -4321,10 +4321,10 @@
         <v>30.55</v>
       </c>
       <c r="E6" t="n">
-        <v>30.55</v>
+        <v>31</v>
       </c>
       <c r="F6" t="n">
-        <v>2452706.75</v>
+        <v>2488835</v>
       </c>
     </row>
     <row r="7">
@@ -4345,10 +4345,10 @@
         <v>360</v>
       </c>
       <c r="E7" t="n">
-        <v>360</v>
+        <v>387.25</v>
       </c>
       <c r="F7" t="n">
-        <v>1698120</v>
+        <v>1826658.25</v>
       </c>
     </row>
     <row r="8">
@@ -4393,10 +4393,10 @@
         <v>12.85</v>
       </c>
       <c r="E9" t="n">
-        <v>12.3</v>
+        <v>12.5</v>
       </c>
       <c r="F9" t="n">
-        <v>744211.5</v>
+        <v>756312.5</v>
       </c>
     </row>
     <row r="10">
@@ -4417,10 +4417,10 @@
         <v>9.18</v>
       </c>
       <c r="E10" t="n">
-        <v>9.119999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="F10" t="n">
-        <v>909263.9999999999</v>
+        <v>907270</v>
       </c>
     </row>
     <row r="11">
@@ -4441,10 +4441,10 @@
         <v>15.35</v>
       </c>
       <c r="E11" t="n">
-        <v>15.95</v>
+        <v>16.05</v>
       </c>
       <c r="F11" t="n">
-        <v>1464784.2</v>
+        <v>1473967.8</v>
       </c>
     </row>
     <row r="12">
@@ -4465,10 +4465,10 @@
         <v>55.5</v>
       </c>
       <c r="E12" t="n">
-        <v>46</v>
+        <v>47.05</v>
       </c>
       <c r="F12" t="n">
-        <v>1393708</v>
+        <v>1425520.9</v>
       </c>
     </row>
     <row r="13">

--- a/reports/MyPortfolio_Tracker_Kenya_Dashboard_Output.xlsx
+++ b/reports/MyPortfolio_Tracker_Kenya_Dashboard_Output.xlsx
@@ -820,7 +820,7 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>26192713.69</v>
+        <v>26211339.6</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
@@ -869,10 +869,10 @@
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>1056000</v>
+        <v>1052700</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>4.03165556840781</v>
+        <v>4.016200682852546</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -882,10 +882,10 @@
         </is>
       </c>
       <c r="B11" s="10" t="n">
-        <v>1128750</v>
+        <v>1132500</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>4.309404567083633</v>
+        <v>4.320649067474598</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -898,7 +898,7 @@
         <v>1299375</v>
       </c>
       <c r="C12" s="8" t="n">
-        <v>4.960826187689298</v>
+        <v>4.957300999602477</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -911,7 +911,7 @@
         <v>1288320</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>4.91861979345753</v>
+        <v>4.915124597447129</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -921,10 +921,10 @@
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>2488835</v>
+        <v>2528977.5</v>
       </c>
       <c r="C14" s="8" t="n">
-        <v>9.50201277139986</v>
+        <v>9.648409957650543</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="B15" s="10" t="n">
-        <v>1826658.25</v>
+        <v>1825479</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>6.973917523854703</v>
+        <v>6.964462815933299</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="B16" s="7" t="n">
-        <v>819547.2400000001</v>
+        <v>821503.2000000001</v>
       </c>
       <c r="C16" s="8" t="n">
-        <v>3.128913062234141</v>
+        <v>3.134151907291301</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -960,10 +960,10 @@
         </is>
       </c>
       <c r="B17" s="10" t="n">
-        <v>756312.5</v>
+        <v>738161</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>2.887491952728629</v>
+        <v>2.816189524323281</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -976,7 +976,7 @@
         <v>907270</v>
       </c>
       <c r="C18" s="8" t="n">
-        <v>3.463825897300525</v>
+        <v>3.461364485163513</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -986,10 +986,10 @@
         </is>
       </c>
       <c r="B19" s="10" t="n">
-        <v>1473967.8</v>
+        <v>1469376</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>5.627396295950578</v>
+        <v>5.605879067699386</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -1002,7 +1002,7 @@
         <v>1425520.9</v>
       </c>
       <c r="C20" s="8" t="n">
-        <v>5.442433024968478</v>
+        <v>5.438565604636246</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -1015,7 +1015,7 @@
         <v>2559858</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>9.77316833336485</v>
+        <v>9.76622347069968</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -1028,7 +1028,7 @@
         <v>1112299</v>
       </c>
       <c r="C22" s="8" t="n">
-        <v>4.246597023754204</v>
+        <v>4.243579370510312</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -1041,7 +1041,7 @@
         <v>6050000</v>
       </c>
       <c r="C23" s="11" t="n">
-        <v>23.09802669400308</v>
+        <v>23.08161311984222</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -1054,7 +1054,7 @@
         <v>2000000</v>
       </c>
       <c r="C24" s="8" t="n">
-        <v>7.635711303802671</v>
+        <v>7.630285328873462</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1"/>
@@ -1078,7 +1078,7 @@
         </is>
       </c>
       <c r="B28" s="8" t="n">
-        <v>18.22050611663827</v>
+        <v>18.20927534737675</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -1088,7 +1088,7 @@
         </is>
       </c>
       <c r="B29" s="11" t="n">
-        <v>7.635711303802671</v>
+        <v>7.630285328873462</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -1098,7 +1098,7 @@
         </is>
       </c>
       <c r="B30" s="8" t="n">
-        <v>14.01976535711905</v>
+        <v>14.00980284120999</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -1108,7 +1108,7 @@
         </is>
       </c>
       <c r="B31" s="11" t="n">
-        <v>14.53365521821958</v>
+        <v>14.50580915749914</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="B32" s="8" t="n">
-        <v>23.09802669400308</v>
+        <v>23.08161311984222</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B33" s="11" t="n">
-        <v>12.99032253881747</v>
+        <v>12.91480424754788</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -1138,7 +1138,7 @@
         </is>
       </c>
       <c r="B34" s="8" t="n">
-        <v>9.50201277139986</v>
+        <v>9.648409957650543</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1"/>
@@ -1276,13 +1276,13 @@
         </is>
       </c>
       <c r="C48" s="8" t="n">
-        <v>6.973917523854703</v>
+        <v>6.964462815933299</v>
       </c>
       <c r="D48" s="8" t="n">
         <v>6.666666666666667</v>
       </c>
       <c r="E48" s="8" t="n">
-        <v>0.3072508571880359</v>
+        <v>0.2977961492666319</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1"/>
@@ -1339,13 +1339,13 @@
         </is>
       </c>
       <c r="D54" s="3" t="n">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>387.25</v>
+        <v>387</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>80548</v>
+        <v>78174</v>
       </c>
       <c r="G54" s="15" t="inlineStr">
         <is>
@@ -1370,13 +1370,13 @@
         </is>
       </c>
       <c r="D55" s="16" t="n">
-        <v>6439</v>
+        <v>6399</v>
       </c>
       <c r="E55" s="10" t="n">
-        <v>12.5</v>
+        <v>12.2</v>
       </c>
       <c r="F55" s="10" t="n">
-        <v>80487.5</v>
+        <v>78067.79999999999</v>
       </c>
       <c r="G55" s="17" t="inlineStr">
         <is>
@@ -1528,13 +1528,13 @@
         <v>32.1</v>
       </c>
       <c r="G2" s="23" t="n">
-        <v>32</v>
+        <v>31.9</v>
       </c>
       <c r="H2" s="19" t="n">
         <v>1059300</v>
       </c>
       <c r="I2" s="23" t="n">
-        <v>1056000</v>
+        <v>1052700</v>
       </c>
       <c r="J2" s="23" t="n">
         <v>66000</v>
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="L2" s="19" t="n">
-        <v>32</v>
+        <v>31.9</v>
       </c>
       <c r="M2" s="19" t="inlineStr">
         <is>
@@ -1554,14 +1554,14 @@
       </c>
       <c r="N2" s="19" t="inlineStr">
         <is>
-          <t>2026-06-02 21:41:29</t>
+          <t>2026-06-03 10:17:26</t>
         </is>
       </c>
       <c r="O2" s="24" t="n">
-        <v>4.03165556840781</v>
+        <v>4.016200682852546</v>
       </c>
       <c r="P2" s="24" t="n">
-        <v>-0.3115264797507832</v>
+        <v>-0.6230529595015665</v>
       </c>
     </row>
     <row r="3">
@@ -1588,13 +1588,13 @@
         <v>74.25</v>
       </c>
       <c r="G3" s="27" t="n">
-        <v>75.25</v>
+        <v>75.5</v>
       </c>
       <c r="H3" s="17" t="n">
         <v>1113750</v>
       </c>
       <c r="I3" s="27" t="n">
-        <v>1128750</v>
+        <v>1132500</v>
       </c>
       <c r="J3" s="27" t="n">
         <v>30000</v>
@@ -1605,7 +1605,7 @@
         </is>
       </c>
       <c r="L3" s="17" t="n">
-        <v>75.25</v>
+        <v>75.5</v>
       </c>
       <c r="M3" s="17" t="inlineStr">
         <is>
@@ -1614,14 +1614,14 @@
       </c>
       <c r="N3" s="17" t="inlineStr">
         <is>
-          <t>2026-06-02 21:41:29</t>
+          <t>2026-06-03 10:17:26</t>
         </is>
       </c>
       <c r="O3" s="28" t="n">
-        <v>4.309404567083633</v>
+        <v>4.320649067474598</v>
       </c>
       <c r="P3" s="28" t="n">
-        <v>1.346801346801347</v>
+        <v>1.683501683501683</v>
       </c>
     </row>
     <row r="4">
@@ -1672,11 +1672,11 @@
       </c>
       <c r="N4" s="19" t="inlineStr">
         <is>
-          <t>2026-06-02 21:41:29</t>
+          <t>2026-06-03 10:17:26</t>
         </is>
       </c>
       <c r="O4" s="24" t="n">
-        <v>4.960826187689298</v>
+        <v>4.957300999602477</v>
       </c>
       <c r="P4" s="24" t="n">
         <v>2.99625468164794</v>
@@ -1732,11 +1732,11 @@
       </c>
       <c r="N5" s="17" t="inlineStr">
         <is>
-          <t>2026-06-02 21:41:29</t>
+          <t>2026-06-03 10:17:26</t>
         </is>
       </c>
       <c r="O5" s="28" t="n">
-        <v>4.91861979345753</v>
+        <v>4.915124597447129</v>
       </c>
       <c r="P5" s="28" t="n">
         <v>0.8595988538681949</v>
@@ -1766,13 +1766,13 @@
         <v>30.55</v>
       </c>
       <c r="G6" s="23" t="n">
-        <v>31</v>
+        <v>31.5</v>
       </c>
       <c r="H6" s="19" t="n">
         <v>2452706.75</v>
       </c>
       <c r="I6" s="23" t="n">
-        <v>2488835</v>
+        <v>2528977.5</v>
       </c>
       <c r="J6" s="23" t="n">
         <v>160570</v>
@@ -1783,7 +1783,7 @@
         </is>
       </c>
       <c r="L6" s="19" t="n">
-        <v>31</v>
+        <v>31.5</v>
       </c>
       <c r="M6" s="19" t="inlineStr">
         <is>
@@ -1792,14 +1792,14 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>2026-06-02 21:41:29</t>
+          <t>2026-06-03 10:17:26</t>
         </is>
       </c>
       <c r="O6" s="24" t="n">
-        <v>9.50201277139986</v>
+        <v>9.648409957650543</v>
       </c>
       <c r="P6" s="24" t="n">
-        <v>1.472995090016364</v>
+        <v>3.10965630114566</v>
       </c>
     </row>
     <row r="7">
@@ -1826,13 +1826,13 @@
         <v>360</v>
       </c>
       <c r="G7" s="27" t="n">
-        <v>387.25</v>
+        <v>387</v>
       </c>
       <c r="H7" s="17" t="n">
         <v>1698120</v>
       </c>
       <c r="I7" s="27" t="n">
-        <v>1826658.25</v>
+        <v>1825479</v>
       </c>
       <c r="J7" s="27" t="n">
         <v>9434</v>
@@ -1843,7 +1843,7 @@
         </is>
       </c>
       <c r="L7" s="17" t="n">
-        <v>387.25</v>
+        <v>387</v>
       </c>
       <c r="M7" s="17" t="inlineStr">
         <is>
@@ -1852,14 +1852,14 @@
       </c>
       <c r="N7" s="17" t="inlineStr">
         <is>
-          <t>2026-06-02 21:41:29</t>
+          <t>2026-06-03 10:17:26</t>
         </is>
       </c>
       <c r="O7" s="28" t="n">
-        <v>6.973917523854703</v>
+        <v>6.964462815933299</v>
       </c>
       <c r="P7" s="28" t="n">
-        <v>7.569444444444444</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="8">
@@ -1886,13 +1886,13 @@
         <v>4.19</v>
       </c>
       <c r="G8" s="23" t="n">
-        <v>4.19</v>
+        <v>4.2</v>
       </c>
       <c r="H8" s="19" t="n">
         <v>819547.2400000001</v>
       </c>
       <c r="I8" s="23" t="n">
-        <v>819547.2400000001</v>
+        <v>821503.2000000001</v>
       </c>
       <c r="J8" s="23" t="n">
         <v>391191.9999999999</v>
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="L8" s="19" t="n">
-        <v>4.19</v>
+        <v>4.2</v>
       </c>
       <c r="M8" s="19" t="inlineStr">
         <is>
@@ -1912,14 +1912,14 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>2026-06-02 21:41:29</t>
+          <t>2026-06-03 10:17:26</t>
         </is>
       </c>
       <c r="O8" s="24" t="n">
-        <v>3.128913062234141</v>
+        <v>3.134151907291301</v>
       </c>
       <c r="P8" s="24" t="n">
-        <v>0</v>
+        <v>0.2386634844868684</v>
       </c>
     </row>
     <row r="9">
@@ -1946,13 +1946,13 @@
         <v>12.85</v>
       </c>
       <c r="G9" s="27" t="n">
-        <v>12.5</v>
+        <v>12.2</v>
       </c>
       <c r="H9" s="17" t="n">
         <v>777489.25</v>
       </c>
       <c r="I9" s="27" t="n">
-        <v>756312.5</v>
+        <v>738161</v>
       </c>
       <c r="J9" s="27" t="n">
         <v>121010</v>
@@ -1963,7 +1963,7 @@
         </is>
       </c>
       <c r="L9" s="17" t="n">
-        <v>12.5</v>
+        <v>12.2</v>
       </c>
       <c r="M9" s="17" t="inlineStr">
         <is>
@@ -1972,14 +1972,14 @@
       </c>
       <c r="N9" s="17" t="inlineStr">
         <is>
-          <t>2026-06-02 21:41:29</t>
+          <t>2026-06-03 10:17:26</t>
         </is>
       </c>
       <c r="O9" s="28" t="n">
-        <v>2.887491952728629</v>
+        <v>2.816189524323281</v>
       </c>
       <c r="P9" s="28" t="n">
-        <v>-2.723735408560309</v>
+        <v>-5.058365758754866</v>
       </c>
     </row>
     <row r="10">
@@ -2032,11 +2032,11 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>2026-06-02 21:41:29</t>
+          <t>2026-06-03 10:17:26</t>
         </is>
       </c>
       <c r="O10" s="24" t="n">
-        <v>3.463825897300525</v>
+        <v>3.461364485163513</v>
       </c>
       <c r="P10" s="24" t="n">
         <v>-0.8714596949891076</v>
@@ -2066,13 +2066,13 @@
         <v>15.35</v>
       </c>
       <c r="G11" s="27" t="n">
-        <v>16.05</v>
+        <v>16</v>
       </c>
       <c r="H11" s="17" t="n">
         <v>1409682.6</v>
       </c>
       <c r="I11" s="27" t="n">
-        <v>1473967.8</v>
+        <v>1469376</v>
       </c>
       <c r="J11" s="27" t="n">
         <v>183672.0000000002</v>
@@ -2083,7 +2083,7 @@
         </is>
       </c>
       <c r="L11" s="17" t="n">
-        <v>16.05</v>
+        <v>16</v>
       </c>
       <c r="M11" s="17" t="inlineStr">
         <is>
@@ -2092,14 +2092,14 @@
       </c>
       <c r="N11" s="17" t="inlineStr">
         <is>
-          <t>2026-06-02 21:41:29</t>
+          <t>2026-06-03 10:17:26</t>
         </is>
       </c>
       <c r="O11" s="28" t="n">
-        <v>5.627396295950578</v>
+        <v>5.605879067699386</v>
       </c>
       <c r="P11" s="28" t="n">
-        <v>4.560260586319225</v>
+        <v>4.23452768729642</v>
       </c>
     </row>
     <row r="12">
@@ -2152,11 +2152,11 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>2026-06-02 21:41:29</t>
+          <t>2026-06-03 10:17:26</t>
         </is>
       </c>
       <c r="O12" s="24" t="n">
-        <v>5.442433024968478</v>
+        <v>5.438565604636246</v>
       </c>
       <c r="P12" s="24" t="n">
         <v>-15.22522522522523</v>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="N13" s="17" t="inlineStr"/>
       <c r="O13" s="28" t="n">
-        <v>9.77316833336485</v>
+        <v>9.76622347069968</v>
       </c>
       <c r="P13" s="28" t="n">
         <v>0.003828483920367535</v>
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr"/>
       <c r="O14" s="24" t="n">
-        <v>4.246597023754204</v>
+        <v>4.243579370510312</v>
       </c>
       <c r="P14" s="24" t="n">
         <v>0.01744439598778892</v>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="N15" s="17" t="inlineStr"/>
       <c r="O15" s="28" t="n">
-        <v>23.09802669400308</v>
+        <v>23.08161311984222</v>
       </c>
       <c r="P15" s="28" t="n">
         <v>0</v>
@@ -2356,7 +2356,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr"/>
       <c r="O16" s="24" t="n">
-        <v>7.635711303802671</v>
+        <v>7.630285328873462</v>
       </c>
       <c r="P16" s="24" t="n">
         <v>0</v>
@@ -2443,7 +2443,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="23" t="n">
-        <v>1056000</v>
+        <v>1052700</v>
       </c>
       <c r="H2" s="19" t="n">
         <v>0</v>
@@ -2465,7 +2465,7 @@
         <v>0</v>
       </c>
       <c r="G3" s="27" t="n">
-        <v>1128750</v>
+        <v>1132500</v>
       </c>
       <c r="H3" s="17" t="n">
         <v>0</v>
@@ -2531,7 +2531,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="23" t="n">
-        <v>2488835</v>
+        <v>2528977.5</v>
       </c>
       <c r="H6" s="19" t="n">
         <v>0</v>
@@ -2553,7 +2553,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="27" t="n">
-        <v>1826658.25</v>
+        <v>1825479</v>
       </c>
       <c r="H7" s="17" t="n">
         <v>0</v>
@@ -2575,7 +2575,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="23" t="n">
-        <v>819547.2400000001</v>
+        <v>821503.2000000001</v>
       </c>
       <c r="H8" s="19" t="n">
         <v>0</v>
@@ -2597,7 +2597,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="27" t="n">
-        <v>756312.5</v>
+        <v>738161</v>
       </c>
       <c r="H9" s="17" t="n">
         <v>0</v>
@@ -2826,11 +2826,11 @@
     <row r="2">
       <c r="A2" s="21" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>26192713.69</v>
+        <v>26211339.6</v>
       </c>
       <c r="C2" s="23" t="inlineStr">
         <is>
@@ -3029,7 +3029,7 @@
         </is>
       </c>
       <c r="C2" s="23" t="n">
-        <v>32</v>
+        <v>31.9</v>
       </c>
       <c r="D2" s="19" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
       </c>
       <c r="E2" s="19" t="inlineStr">
         <is>
-          <t>2026-06-02 21:41:29</t>
+          <t>2026-06-03 10:17:26</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
         </is>
       </c>
       <c r="C3" s="27" t="n">
-        <v>75.25</v>
+        <v>75.5</v>
       </c>
       <c r="D3" s="17" t="inlineStr">
         <is>
@@ -3063,7 +3063,7 @@
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>2026-06-02 21:41:29</t>
+          <t>2026-06-03 10:17:26</t>
         </is>
       </c>
     </row>
@@ -3088,7 +3088,7 @@
       </c>
       <c r="E4" s="19" t="inlineStr">
         <is>
-          <t>2026-06-02 21:41:29</t>
+          <t>2026-06-03 10:17:26</t>
         </is>
       </c>
     </row>
@@ -3113,7 +3113,7 @@
       </c>
       <c r="E5" s="17" t="inlineStr">
         <is>
-          <t>2026-06-02 21:41:29</t>
+          <t>2026-06-03 10:17:26</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="C6" s="23" t="n">
-        <v>31</v>
+        <v>31.5</v>
       </c>
       <c r="D6" s="19" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="E6" s="19" t="inlineStr">
         <is>
-          <t>2026-06-02 21:41:29</t>
+          <t>2026-06-03 10:17:26</t>
         </is>
       </c>
     </row>
@@ -3154,7 +3154,7 @@
         </is>
       </c>
       <c r="C7" s="27" t="n">
-        <v>387.25</v>
+        <v>387</v>
       </c>
       <c r="D7" s="17" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
       </c>
       <c r="E7" s="17" t="inlineStr">
         <is>
-          <t>2026-06-02 21:41:29</t>
+          <t>2026-06-03 10:17:26</t>
         </is>
       </c>
     </row>
@@ -3179,7 +3179,7 @@
         </is>
       </c>
       <c r="C8" s="23" t="n">
-        <v>4.19</v>
+        <v>4.2</v>
       </c>
       <c r="D8" s="19" t="inlineStr">
         <is>
@@ -3188,7 +3188,7 @@
       </c>
       <c r="E8" s="19" t="inlineStr">
         <is>
-          <t>2026-06-02 21:41:29</t>
+          <t>2026-06-03 10:17:26</t>
         </is>
       </c>
     </row>
@@ -3204,7 +3204,7 @@
         </is>
       </c>
       <c r="C9" s="27" t="n">
-        <v>12.5</v>
+        <v>12.2</v>
       </c>
       <c r="D9" s="17" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="E9" s="17" t="inlineStr">
         <is>
-          <t>2026-06-02 21:41:29</t>
+          <t>2026-06-03 10:17:26</t>
         </is>
       </c>
     </row>
@@ -3238,7 +3238,7 @@
       </c>
       <c r="E10" s="19" t="inlineStr">
         <is>
-          <t>2026-06-02 21:41:29</t>
+          <t>2026-06-03 10:17:26</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
         </is>
       </c>
       <c r="C11" s="27" t="n">
-        <v>16.05</v>
+        <v>16</v>
       </c>
       <c r="D11" s="17" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="E11" s="17" t="inlineStr">
         <is>
-          <t>2026-06-02 21:41:29</t>
+          <t>2026-06-03 10:17:26</t>
         </is>
       </c>
     </row>
@@ -3288,7 +3288,7 @@
       </c>
       <c r="E12" s="19" t="inlineStr">
         <is>
-          <t>2026-06-02 21:41:29</t>
+          <t>2026-06-03 10:17:26</t>
         </is>
       </c>
     </row>
@@ -3459,7 +3459,7 @@
     <row r="2">
       <c r="A2" s="21" t="inlineStr">
         <is>
-          <t>2026-06-02 21:42:18</t>
+          <t>2026-06-03 10:18:15</t>
         </is>
       </c>
       <c r="B2" s="21" t="inlineStr">
@@ -3491,7 +3491,7 @@
         <v>0</v>
       </c>
       <c r="J2" s="23" t="n">
-        <v>-3300</v>
+        <v>-6600</v>
       </c>
       <c r="K2" s="23" t="n">
         <v>1059300</v>
@@ -3506,7 +3506,7 @@
     <row r="3">
       <c r="A3" s="25" t="inlineStr">
         <is>
-          <t>2026-06-02 21:42:18</t>
+          <t>2026-06-03 10:18:15</t>
         </is>
       </c>
       <c r="B3" s="25" t="inlineStr">
@@ -3538,7 +3538,7 @@
         <v>0</v>
       </c>
       <c r="J3" s="27" t="n">
-        <v>15000</v>
+        <v>18750</v>
       </c>
       <c r="K3" s="27" t="n">
         <v>1113750</v>
@@ -3553,7 +3553,7 @@
     <row r="4">
       <c r="A4" s="21" t="inlineStr">
         <is>
-          <t>2026-06-02 21:42:18</t>
+          <t>2026-06-03 10:18:15</t>
         </is>
       </c>
       <c r="B4" s="21" t="inlineStr">
@@ -3600,7 +3600,7 @@
     <row r="5">
       <c r="A5" s="25" t="inlineStr">
         <is>
-          <t>2026-06-02 21:42:18</t>
+          <t>2026-06-03 10:18:15</t>
         </is>
       </c>
       <c r="B5" s="25" t="inlineStr">
@@ -3647,7 +3647,7 @@
     <row r="6">
       <c r="A6" s="21" t="inlineStr">
         <is>
-          <t>2026-06-02 21:42:18</t>
+          <t>2026-06-03 10:18:15</t>
         </is>
       </c>
       <c r="B6" s="21" t="inlineStr">
@@ -3679,7 +3679,7 @@
         <v>0</v>
       </c>
       <c r="J6" s="23" t="n">
-        <v>36128.25</v>
+        <v>76270.75</v>
       </c>
       <c r="K6" s="23" t="n">
         <v>2452706.75</v>
@@ -3694,7 +3694,7 @@
     <row r="7">
       <c r="A7" s="25" t="inlineStr">
         <is>
-          <t>2026-06-02 21:42:18</t>
+          <t>2026-06-03 10:18:15</t>
         </is>
       </c>
       <c r="B7" s="25" t="inlineStr">
@@ -3726,7 +3726,7 @@
         <v>0</v>
       </c>
       <c r="J7" s="27" t="n">
-        <v>128538.25</v>
+        <v>127359</v>
       </c>
       <c r="K7" s="27" t="n">
         <v>1698120</v>
@@ -3741,7 +3741,7 @@
     <row r="8">
       <c r="A8" s="21" t="inlineStr">
         <is>
-          <t>2026-06-02 21:42:18</t>
+          <t>2026-06-03 10:18:15</t>
         </is>
       </c>
       <c r="B8" s="21" t="inlineStr">
@@ -3773,7 +3773,7 @@
         <v>0</v>
       </c>
       <c r="J8" s="23" t="n">
-        <v>0</v>
+        <v>1955.959999999963</v>
       </c>
       <c r="K8" s="23" t="n">
         <v>819547.2400000001</v>
@@ -3788,7 +3788,7 @@
     <row r="9">
       <c r="A9" s="25" t="inlineStr">
         <is>
-          <t>2026-06-02 21:42:18</t>
+          <t>2026-06-03 10:18:15</t>
         </is>
       </c>
       <c r="B9" s="25" t="inlineStr">
@@ -3820,7 +3820,7 @@
         <v>0</v>
       </c>
       <c r="J9" s="27" t="n">
-        <v>-21176.75</v>
+        <v>-39328.25</v>
       </c>
       <c r="K9" s="27" t="n">
         <v>777489.25</v>
@@ -3835,7 +3835,7 @@
     <row r="10">
       <c r="A10" s="21" t="inlineStr">
         <is>
-          <t>2026-06-02 21:42:18</t>
+          <t>2026-06-03 10:18:15</t>
         </is>
       </c>
       <c r="B10" s="21" t="inlineStr">
@@ -3882,7 +3882,7 @@
     <row r="11">
       <c r="A11" s="25" t="inlineStr">
         <is>
-          <t>2026-06-02 21:42:18</t>
+          <t>2026-06-03 10:18:15</t>
         </is>
       </c>
       <c r="B11" s="25" t="inlineStr">
@@ -3914,7 +3914,7 @@
         <v>0</v>
       </c>
       <c r="J11" s="27" t="n">
-        <v>64285.20000000019</v>
+        <v>59693.40000000014</v>
       </c>
       <c r="K11" s="27" t="n">
         <v>1409682.6</v>
@@ -3929,7 +3929,7 @@
     <row r="12">
       <c r="A12" s="21" t="inlineStr">
         <is>
-          <t>2026-06-02 21:42:18</t>
+          <t>2026-06-03 10:18:15</t>
         </is>
       </c>
       <c r="B12" s="21" t="inlineStr">
@@ -3976,7 +3976,7 @@
     <row r="13">
       <c r="A13" s="25" t="inlineStr">
         <is>
-          <t>2026-06-02 21:42:18</t>
+          <t>2026-06-03 10:18:15</t>
         </is>
       </c>
       <c r="B13" s="25" t="inlineStr">
@@ -4023,7 +4023,7 @@
     <row r="14">
       <c r="A14" s="21" t="inlineStr">
         <is>
-          <t>2026-06-02 21:42:18</t>
+          <t>2026-06-03 10:18:15</t>
         </is>
       </c>
       <c r="B14" s="21" t="inlineStr">
@@ -4070,7 +4070,7 @@
     <row r="15">
       <c r="A15" s="25" t="inlineStr">
         <is>
-          <t>2026-06-02 21:42:18</t>
+          <t>2026-06-03 10:18:15</t>
         </is>
       </c>
       <c r="B15" s="25" t="inlineStr">
@@ -4117,7 +4117,7 @@
     <row r="16">
       <c r="A16" s="21" t="inlineStr">
         <is>
-          <t>2026-06-02 21:42:18</t>
+          <t>2026-06-03 10:18:15</t>
         </is>
       </c>
       <c r="B16" s="21" t="inlineStr">
@@ -4225,10 +4225,10 @@
         <v>32.1</v>
       </c>
       <c r="E2" t="n">
-        <v>32</v>
+        <v>31.9</v>
       </c>
       <c r="F2" t="n">
-        <v>1056000</v>
+        <v>1052700</v>
       </c>
     </row>
     <row r="3">
@@ -4249,10 +4249,10 @@
         <v>74.25</v>
       </c>
       <c r="E3" t="n">
-        <v>75.25</v>
+        <v>75.5</v>
       </c>
       <c r="F3" t="n">
-        <v>1128750</v>
+        <v>1132500</v>
       </c>
     </row>
     <row r="4">
@@ -4321,10 +4321,10 @@
         <v>30.55</v>
       </c>
       <c r="E6" t="n">
-        <v>31</v>
+        <v>31.5</v>
       </c>
       <c r="F6" t="n">
-        <v>2488835</v>
+        <v>2528977.5</v>
       </c>
     </row>
     <row r="7">
@@ -4345,10 +4345,10 @@
         <v>360</v>
       </c>
       <c r="E7" t="n">
-        <v>387.25</v>
+        <v>387</v>
       </c>
       <c r="F7" t="n">
-        <v>1826658.25</v>
+        <v>1825479</v>
       </c>
     </row>
     <row r="8">
@@ -4369,10 +4369,10 @@
         <v>4.19</v>
       </c>
       <c r="E8" t="n">
-        <v>4.19</v>
+        <v>4.2</v>
       </c>
       <c r="F8" t="n">
-        <v>819547.2400000001</v>
+        <v>821503.2000000001</v>
       </c>
     </row>
     <row r="9">
@@ -4393,10 +4393,10 @@
         <v>12.85</v>
       </c>
       <c r="E9" t="n">
-        <v>12.5</v>
+        <v>12.2</v>
       </c>
       <c r="F9" t="n">
-        <v>756312.5</v>
+        <v>738161</v>
       </c>
     </row>
     <row r="10">
@@ -4441,10 +4441,10 @@
         <v>15.35</v>
       </c>
       <c r="E11" t="n">
-        <v>16.05</v>
+        <v>16</v>
       </c>
       <c r="F11" t="n">
-        <v>1473967.8</v>
+        <v>1469376</v>
       </c>
     </row>
     <row r="12">

--- a/reports/MyPortfolio_Tracker_Kenya_Dashboard_Output.xlsx
+++ b/reports/MyPortfolio_Tracker_Kenya_Dashboard_Output.xlsx
@@ -820,7 +820,7 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>26211339.6</v>
+        <v>26594408.94</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
@@ -869,10 +869,10 @@
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>1052700</v>
+        <v>1049400</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>4.016200682852546</v>
+        <v>3.945942180431854</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -882,10 +882,10 @@
         </is>
       </c>
       <c r="B11" s="10" t="n">
-        <v>1132500</v>
+        <v>1162500</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>4.320649067474598</v>
+        <v>4.371219539500697</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -898,7 +898,7 @@
         <v>1299375</v>
       </c>
       <c r="C12" s="8" t="n">
-        <v>4.957300999602477</v>
+        <v>4.885895388506424</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -908,10 +908,10 @@
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>1288320</v>
+        <v>1299300</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>4.915124597447129</v>
+        <v>4.885613374342586</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -921,10 +921,10 @@
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>2528977.5</v>
+        <v>2524963.25</v>
       </c>
       <c r="C14" s="8" t="n">
-        <v>9.648409957650543</v>
+        <v>9.494338662297791</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="B15" s="10" t="n">
-        <v>1825479</v>
+        <v>1872649</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>6.964462815933299</v>
+        <v>7.041513891979734</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="B16" s="7" t="n">
-        <v>821503.2000000001</v>
+        <v>819547.2400000001</v>
       </c>
       <c r="C16" s="8" t="n">
-        <v>3.134151907291301</v>
+        <v>3.081652394866123</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -960,10 +960,10 @@
         </is>
       </c>
       <c r="B17" s="10" t="n">
-        <v>738161</v>
+        <v>753287.25</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>2.816189524323281</v>
+        <v>2.832502319188599</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -976,7 +976,7 @@
         <v>907270</v>
       </c>
       <c r="C18" s="8" t="n">
-        <v>3.461364485163513</v>
+        <v>3.411506539013159</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -986,10 +986,10 @@
         </is>
       </c>
       <c r="B19" s="10" t="n">
-        <v>1469376</v>
+        <v>1441825.2</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>5.605879067699386</v>
+        <v>5.421535042395269</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -999,10 +999,10 @@
         </is>
       </c>
       <c r="B20" s="7" t="n">
-        <v>1425520.9</v>
+        <v>1742135</v>
       </c>
       <c r="C20" s="8" t="n">
-        <v>5.438565604636246</v>
+        <v>6.550756604256384</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -1015,7 +1015,7 @@
         <v>2559858</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>9.76622347069968</v>
+        <v>9.625549512212624</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -1028,7 +1028,7 @@
         <v>1112299</v>
       </c>
       <c r="C22" s="8" t="n">
-        <v>4.243579370510312</v>
+        <v>4.182454298982439</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -1041,7 +1041,7 @@
         <v>6050000</v>
       </c>
       <c r="C23" s="11" t="n">
-        <v>23.08161311984222</v>
+        <v>22.74914254965954</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -1054,7 +1054,7 @@
         <v>2000000</v>
       </c>
       <c r="C24" s="8" t="n">
-        <v>7.630285328873462</v>
+        <v>7.52037770236679</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1"/>
@@ -1078,7 +1078,7 @@
         </is>
       </c>
       <c r="B28" s="8" t="n">
-        <v>18.20927534737675</v>
+        <v>18.08867048278156</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -1088,7 +1088,7 @@
         </is>
       </c>
       <c r="B29" s="11" t="n">
-        <v>7.630285328873462</v>
+        <v>7.52037770236679</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -1098,7 +1098,7 @@
         </is>
       </c>
       <c r="B30" s="8" t="n">
-        <v>14.00980284120999</v>
+        <v>13.80800381119506</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -1108,7 +1108,7 @@
         </is>
       </c>
       <c r="B31" s="11" t="n">
-        <v>14.50580915749914</v>
+        <v>15.38379818566481</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="B32" s="8" t="n">
-        <v>23.08161311984222</v>
+        <v>22.74914254965954</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B33" s="11" t="n">
-        <v>12.91480424754788</v>
+        <v>12.95566860603445</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -1138,7 +1138,7 @@
         </is>
       </c>
       <c r="B34" s="8" t="n">
-        <v>9.648409957650543</v>
+        <v>9.494338662297791</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1"/>
@@ -1276,13 +1276,13 @@
         </is>
       </c>
       <c r="C48" s="8" t="n">
-        <v>6.964462815933299</v>
+        <v>7.041513891979734</v>
       </c>
       <c r="D48" s="8" t="n">
         <v>6.666666666666667</v>
       </c>
       <c r="E48" s="8" t="n">
-        <v>0.2977961492666319</v>
+        <v>0.3748472253130668</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1"/>
@@ -1339,13 +1339,13 @@
         </is>
       </c>
       <c r="D54" s="3" t="n">
-        <v>202</v>
+        <v>252</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>387</v>
+        <v>397</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>78174</v>
+        <v>100044</v>
       </c>
       <c r="G54" s="15" t="inlineStr">
         <is>
@@ -1370,13 +1370,13 @@
         </is>
       </c>
       <c r="D55" s="16" t="n">
-        <v>6399</v>
+        <v>8008</v>
       </c>
       <c r="E55" s="10" t="n">
-        <v>12.2</v>
+        <v>12.45</v>
       </c>
       <c r="F55" s="10" t="n">
-        <v>78067.79999999999</v>
+        <v>99699.59999999999</v>
       </c>
       <c r="G55" s="17" t="inlineStr">
         <is>
@@ -1528,13 +1528,13 @@
         <v>32.1</v>
       </c>
       <c r="G2" s="23" t="n">
-        <v>31.9</v>
+        <v>31.8</v>
       </c>
       <c r="H2" s="19" t="n">
         <v>1059300</v>
       </c>
       <c r="I2" s="23" t="n">
-        <v>1052700</v>
+        <v>1049400</v>
       </c>
       <c r="J2" s="23" t="n">
         <v>66000</v>
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="L2" s="19" t="n">
-        <v>31.9</v>
+        <v>31.8</v>
       </c>
       <c r="M2" s="19" t="inlineStr">
         <is>
@@ -1554,14 +1554,14 @@
       </c>
       <c r="N2" s="19" t="inlineStr">
         <is>
-          <t>2026-06-03 10:17:26</t>
+          <t>2026-06-05 02:02:19</t>
         </is>
       </c>
       <c r="O2" s="24" t="n">
-        <v>4.016200682852546</v>
+        <v>3.945942180431854</v>
       </c>
       <c r="P2" s="24" t="n">
-        <v>-0.6230529595015665</v>
+        <v>-0.9345794392523387</v>
       </c>
     </row>
     <row r="3">
@@ -1588,13 +1588,13 @@
         <v>74.25</v>
       </c>
       <c r="G3" s="27" t="n">
-        <v>75.5</v>
+        <v>77.5</v>
       </c>
       <c r="H3" s="17" t="n">
         <v>1113750</v>
       </c>
       <c r="I3" s="27" t="n">
-        <v>1132500</v>
+        <v>1162500</v>
       </c>
       <c r="J3" s="27" t="n">
         <v>30000</v>
@@ -1605,7 +1605,7 @@
         </is>
       </c>
       <c r="L3" s="17" t="n">
-        <v>75.5</v>
+        <v>77.5</v>
       </c>
       <c r="M3" s="17" t="inlineStr">
         <is>
@@ -1614,14 +1614,14 @@
       </c>
       <c r="N3" s="17" t="inlineStr">
         <is>
-          <t>2026-06-03 10:17:26</t>
+          <t>2026-06-05 02:02:19</t>
         </is>
       </c>
       <c r="O3" s="28" t="n">
-        <v>4.320649067474598</v>
+        <v>4.371219539500697</v>
       </c>
       <c r="P3" s="28" t="n">
-        <v>1.683501683501683</v>
+        <v>4.377104377104377</v>
       </c>
     </row>
     <row r="4">
@@ -1672,11 +1672,11 @@
       </c>
       <c r="N4" s="19" t="inlineStr">
         <is>
-          <t>2026-06-03 10:17:26</t>
+          <t>2026-06-05 02:02:19</t>
         </is>
       </c>
       <c r="O4" s="24" t="n">
-        <v>4.957300999602477</v>
+        <v>4.885895388506424</v>
       </c>
       <c r="P4" s="24" t="n">
         <v>2.99625468164794</v>
@@ -1706,13 +1706,13 @@
         <v>87.25</v>
       </c>
       <c r="G5" s="27" t="n">
-        <v>88</v>
+        <v>88.75</v>
       </c>
       <c r="H5" s="17" t="n">
         <v>1277340</v>
       </c>
       <c r="I5" s="27" t="n">
-        <v>1288320</v>
+        <v>1299300</v>
       </c>
       <c r="J5" s="27" t="n">
         <v>29280</v>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="L5" s="17" t="n">
-        <v>88</v>
+        <v>88.75</v>
       </c>
       <c r="M5" s="17" t="inlineStr">
         <is>
@@ -1732,14 +1732,14 @@
       </c>
       <c r="N5" s="17" t="inlineStr">
         <is>
-          <t>2026-06-03 10:17:26</t>
+          <t>2026-06-05 02:02:19</t>
         </is>
       </c>
       <c r="O5" s="28" t="n">
-        <v>4.915124597447129</v>
+        <v>4.885613374342586</v>
       </c>
       <c r="P5" s="28" t="n">
-        <v>0.8595988538681949</v>
+        <v>1.71919770773639</v>
       </c>
     </row>
     <row r="6">
@@ -1766,13 +1766,13 @@
         <v>30.55</v>
       </c>
       <c r="G6" s="23" t="n">
-        <v>31.5</v>
+        <v>31.45</v>
       </c>
       <c r="H6" s="19" t="n">
         <v>2452706.75</v>
       </c>
       <c r="I6" s="23" t="n">
-        <v>2528977.5</v>
+        <v>2524963.25</v>
       </c>
       <c r="J6" s="23" t="n">
         <v>160570</v>
@@ -1783,7 +1783,7 @@
         </is>
       </c>
       <c r="L6" s="19" t="n">
-        <v>31.5</v>
+        <v>31.45</v>
       </c>
       <c r="M6" s="19" t="inlineStr">
         <is>
@@ -1792,14 +1792,14 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>2026-06-03 10:17:26</t>
+          <t>2026-06-05 02:02:19</t>
         </is>
       </c>
       <c r="O6" s="24" t="n">
-        <v>9.648409957650543</v>
+        <v>9.494338662297791</v>
       </c>
       <c r="P6" s="24" t="n">
-        <v>3.10965630114566</v>
+        <v>2.945990180032728</v>
       </c>
     </row>
     <row r="7">
@@ -1826,13 +1826,13 @@
         <v>360</v>
       </c>
       <c r="G7" s="27" t="n">
-        <v>387</v>
+        <v>397</v>
       </c>
       <c r="H7" s="17" t="n">
         <v>1698120</v>
       </c>
       <c r="I7" s="27" t="n">
-        <v>1825479</v>
+        <v>1872649</v>
       </c>
       <c r="J7" s="27" t="n">
         <v>9434</v>
@@ -1843,7 +1843,7 @@
         </is>
       </c>
       <c r="L7" s="17" t="n">
-        <v>387</v>
+        <v>397</v>
       </c>
       <c r="M7" s="17" t="inlineStr">
         <is>
@@ -1852,14 +1852,14 @@
       </c>
       <c r="N7" s="17" t="inlineStr">
         <is>
-          <t>2026-06-03 10:17:26</t>
+          <t>2026-06-05 02:02:19</t>
         </is>
       </c>
       <c r="O7" s="28" t="n">
-        <v>6.964462815933299</v>
+        <v>7.041513891979734</v>
       </c>
       <c r="P7" s="28" t="n">
-        <v>7.5</v>
+        <v>10.27777777777778</v>
       </c>
     </row>
     <row r="8">
@@ -1886,13 +1886,13 @@
         <v>4.19</v>
       </c>
       <c r="G8" s="23" t="n">
-        <v>4.2</v>
+        <v>4.19</v>
       </c>
       <c r="H8" s="19" t="n">
         <v>819547.2400000001</v>
       </c>
       <c r="I8" s="23" t="n">
-        <v>821503.2000000001</v>
+        <v>819547.2400000001</v>
       </c>
       <c r="J8" s="23" t="n">
         <v>391191.9999999999</v>
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="L8" s="19" t="n">
-        <v>4.2</v>
+        <v>4.19</v>
       </c>
       <c r="M8" s="19" t="inlineStr">
         <is>
@@ -1912,14 +1912,14 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>2026-06-03 10:17:26</t>
+          <t>2026-06-05 02:02:19</t>
         </is>
       </c>
       <c r="O8" s="24" t="n">
-        <v>3.134151907291301</v>
+        <v>3.081652394866123</v>
       </c>
       <c r="P8" s="24" t="n">
-        <v>0.2386634844868684</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1946,13 +1946,13 @@
         <v>12.85</v>
       </c>
       <c r="G9" s="27" t="n">
-        <v>12.2</v>
+        <v>12.45</v>
       </c>
       <c r="H9" s="17" t="n">
         <v>777489.25</v>
       </c>
       <c r="I9" s="27" t="n">
-        <v>738161</v>
+        <v>753287.25</v>
       </c>
       <c r="J9" s="27" t="n">
         <v>121010</v>
@@ -1963,7 +1963,7 @@
         </is>
       </c>
       <c r="L9" s="17" t="n">
-        <v>12.2</v>
+        <v>12.45</v>
       </c>
       <c r="M9" s="17" t="inlineStr">
         <is>
@@ -1972,14 +1972,14 @@
       </c>
       <c r="N9" s="17" t="inlineStr">
         <is>
-          <t>2026-06-03 10:17:26</t>
+          <t>2026-06-05 02:02:19</t>
         </is>
       </c>
       <c r="O9" s="28" t="n">
-        <v>2.816189524323281</v>
+        <v>2.832502319188599</v>
       </c>
       <c r="P9" s="28" t="n">
-        <v>-5.058365758754866</v>
+        <v>-3.112840466926073</v>
       </c>
     </row>
     <row r="10">
@@ -2032,11 +2032,11 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>2026-06-03 10:17:26</t>
+          <t>2026-06-05 02:02:19</t>
         </is>
       </c>
       <c r="O10" s="24" t="n">
-        <v>3.461364485163513</v>
+        <v>3.411506539013159</v>
       </c>
       <c r="P10" s="24" t="n">
         <v>-0.8714596949891076</v>
@@ -2066,13 +2066,13 @@
         <v>15.35</v>
       </c>
       <c r="G11" s="27" t="n">
-        <v>16</v>
+        <v>15.7</v>
       </c>
       <c r="H11" s="17" t="n">
         <v>1409682.6</v>
       </c>
       <c r="I11" s="27" t="n">
-        <v>1469376</v>
+        <v>1441825.2</v>
       </c>
       <c r="J11" s="27" t="n">
         <v>183672.0000000002</v>
@@ -2083,7 +2083,7 @@
         </is>
       </c>
       <c r="L11" s="17" t="n">
-        <v>16</v>
+        <v>15.7</v>
       </c>
       <c r="M11" s="17" t="inlineStr">
         <is>
@@ -2092,14 +2092,14 @@
       </c>
       <c r="N11" s="17" t="inlineStr">
         <is>
-          <t>2026-06-03 10:17:26</t>
+          <t>2026-06-05 02:02:19</t>
         </is>
       </c>
       <c r="O11" s="28" t="n">
-        <v>5.605879067699386</v>
+        <v>5.421535042395269</v>
       </c>
       <c r="P11" s="28" t="n">
-        <v>4.23452768729642</v>
+        <v>2.280130293159607</v>
       </c>
     </row>
     <row r="12">
@@ -2126,13 +2126,13 @@
         <v>55.5</v>
       </c>
       <c r="G12" s="23" t="n">
-        <v>47.05</v>
+        <v>57.5</v>
       </c>
       <c r="H12" s="19" t="n">
         <v>1681539</v>
       </c>
       <c r="I12" s="23" t="n">
-        <v>1425520.9</v>
+        <v>1742135</v>
       </c>
       <c r="J12" s="23" t="n">
         <v>60596</v>
@@ -2142,24 +2142,22 @@
           <t>TOTL</t>
         </is>
       </c>
-      <c r="L12" s="19" t="n">
-        <v>47.05</v>
-      </c>
+      <c r="L12" s="19" t="inlineStr"/>
       <c r="M12" s="19" t="inlineStr">
         <is>
-          <t>NSE live market data</t>
+          <t>NSE live market data unavailable</t>
         </is>
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>2026-06-03 10:17:26</t>
+          <t>2026-06-05 02:02:19</t>
         </is>
       </c>
       <c r="O12" s="24" t="n">
-        <v>5.438565604636246</v>
+        <v>6.550756604256384</v>
       </c>
       <c r="P12" s="24" t="n">
-        <v>-15.22522522522523</v>
+        <v>3.603603603603604</v>
       </c>
     </row>
     <row r="13">
@@ -2206,7 +2204,7 @@
       </c>
       <c r="N13" s="17" t="inlineStr"/>
       <c r="O13" s="28" t="n">
-        <v>9.76622347069968</v>
+        <v>9.625549512212624</v>
       </c>
       <c r="P13" s="28" t="n">
         <v>0.003828483920367535</v>
@@ -2256,7 +2254,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr"/>
       <c r="O14" s="24" t="n">
-        <v>4.243579370510312</v>
+        <v>4.182454298982439</v>
       </c>
       <c r="P14" s="24" t="n">
         <v>0.01744439598778892</v>
@@ -2306,7 +2304,7 @@
       </c>
       <c r="N15" s="17" t="inlineStr"/>
       <c r="O15" s="28" t="n">
-        <v>23.08161311984222</v>
+        <v>22.74914254965954</v>
       </c>
       <c r="P15" s="28" t="n">
         <v>0</v>
@@ -2356,7 +2354,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr"/>
       <c r="O16" s="24" t="n">
-        <v>7.630285328873462</v>
+        <v>7.52037770236679</v>
       </c>
       <c r="P16" s="24" t="n">
         <v>0</v>
@@ -2443,7 +2441,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="23" t="n">
-        <v>1052700</v>
+        <v>1049400</v>
       </c>
       <c r="H2" s="19" t="n">
         <v>0</v>
@@ -2465,7 +2463,7 @@
         <v>0</v>
       </c>
       <c r="G3" s="27" t="n">
-        <v>1132500</v>
+        <v>1162500</v>
       </c>
       <c r="H3" s="17" t="n">
         <v>0</v>
@@ -2509,7 +2507,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="27" t="n">
-        <v>1288320</v>
+        <v>1299300</v>
       </c>
       <c r="H5" s="17" t="n">
         <v>0</v>
@@ -2531,7 +2529,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="23" t="n">
-        <v>2528977.5</v>
+        <v>2524963.25</v>
       </c>
       <c r="H6" s="19" t="n">
         <v>0</v>
@@ -2553,7 +2551,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="27" t="n">
-        <v>1825479</v>
+        <v>1872649</v>
       </c>
       <c r="H7" s="17" t="n">
         <v>0</v>
@@ -2575,7 +2573,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="23" t="n">
-        <v>821503.2000000001</v>
+        <v>819547.2400000001</v>
       </c>
       <c r="H8" s="19" t="n">
         <v>0</v>
@@ -2597,7 +2595,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="27" t="n">
-        <v>738161</v>
+        <v>753287.25</v>
       </c>
       <c r="H9" s="17" t="n">
         <v>0</v>
@@ -2661,7 +2659,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="23" t="n">
-        <v>1425520.9</v>
+        <v>1742135</v>
       </c>
       <c r="H12" s="19" t="n">
         <v>0</v>
@@ -2826,11 +2824,11 @@
     <row r="2">
       <c r="A2" s="21" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>26211339.6</v>
+        <v>26594408.94</v>
       </c>
       <c r="C2" s="23" t="inlineStr">
         <is>
@@ -3029,7 +3027,7 @@
         </is>
       </c>
       <c r="C2" s="23" t="n">
-        <v>31.9</v>
+        <v>31.8</v>
       </c>
       <c r="D2" s="19" t="inlineStr">
         <is>
@@ -3038,7 +3036,7 @@
       </c>
       <c r="E2" s="19" t="inlineStr">
         <is>
-          <t>2026-06-03 10:17:26</t>
+          <t>2026-06-05 02:02:19</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3052,7 @@
         </is>
       </c>
       <c r="C3" s="27" t="n">
-        <v>75.5</v>
+        <v>77.5</v>
       </c>
       <c r="D3" s="17" t="inlineStr">
         <is>
@@ -3063,7 +3061,7 @@
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>2026-06-03 10:17:26</t>
+          <t>2026-06-05 02:02:19</t>
         </is>
       </c>
     </row>
@@ -3088,7 +3086,7 @@
       </c>
       <c r="E4" s="19" t="inlineStr">
         <is>
-          <t>2026-06-03 10:17:26</t>
+          <t>2026-06-05 02:02:19</t>
         </is>
       </c>
     </row>
@@ -3104,7 +3102,7 @@
         </is>
       </c>
       <c r="C5" s="27" t="n">
-        <v>88</v>
+        <v>88.75</v>
       </c>
       <c r="D5" s="17" t="inlineStr">
         <is>
@@ -3113,7 +3111,7 @@
       </c>
       <c r="E5" s="17" t="inlineStr">
         <is>
-          <t>2026-06-03 10:17:26</t>
+          <t>2026-06-05 02:02:19</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3127,7 @@
         </is>
       </c>
       <c r="C6" s="23" t="n">
-        <v>31.5</v>
+        <v>31.45</v>
       </c>
       <c r="D6" s="19" t="inlineStr">
         <is>
@@ -3138,7 +3136,7 @@
       </c>
       <c r="E6" s="19" t="inlineStr">
         <is>
-          <t>2026-06-03 10:17:26</t>
+          <t>2026-06-05 02:02:19</t>
         </is>
       </c>
     </row>
@@ -3154,7 +3152,7 @@
         </is>
       </c>
       <c r="C7" s="27" t="n">
-        <v>387</v>
+        <v>397</v>
       </c>
       <c r="D7" s="17" t="inlineStr">
         <is>
@@ -3163,7 +3161,7 @@
       </c>
       <c r="E7" s="17" t="inlineStr">
         <is>
-          <t>2026-06-03 10:17:26</t>
+          <t>2026-06-05 02:02:19</t>
         </is>
       </c>
     </row>
@@ -3179,7 +3177,7 @@
         </is>
       </c>
       <c r="C8" s="23" t="n">
-        <v>4.2</v>
+        <v>4.19</v>
       </c>
       <c r="D8" s="19" t="inlineStr">
         <is>
@@ -3188,7 +3186,7 @@
       </c>
       <c r="E8" s="19" t="inlineStr">
         <is>
-          <t>2026-06-03 10:17:26</t>
+          <t>2026-06-05 02:02:19</t>
         </is>
       </c>
     </row>
@@ -3204,7 +3202,7 @@
         </is>
       </c>
       <c r="C9" s="27" t="n">
-        <v>12.2</v>
+        <v>12.45</v>
       </c>
       <c r="D9" s="17" t="inlineStr">
         <is>
@@ -3213,7 +3211,7 @@
       </c>
       <c r="E9" s="17" t="inlineStr">
         <is>
-          <t>2026-06-03 10:17:26</t>
+          <t>2026-06-05 02:02:19</t>
         </is>
       </c>
     </row>
@@ -3238,7 +3236,7 @@
       </c>
       <c r="E10" s="19" t="inlineStr">
         <is>
-          <t>2026-06-03 10:17:26</t>
+          <t>2026-06-05 02:02:19</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3252,7 @@
         </is>
       </c>
       <c r="C11" s="27" t="n">
-        <v>16</v>
+        <v>15.7</v>
       </c>
       <c r="D11" s="17" t="inlineStr">
         <is>
@@ -3263,7 +3261,7 @@
       </c>
       <c r="E11" s="17" t="inlineStr">
         <is>
-          <t>2026-06-03 10:17:26</t>
+          <t>2026-06-05 02:02:19</t>
         </is>
       </c>
     </row>
@@ -3279,16 +3277,16 @@
         </is>
       </c>
       <c r="C12" s="23" t="n">
-        <v>47.05</v>
+        <v>57.5</v>
       </c>
       <c r="D12" s="19" t="inlineStr">
         <is>
-          <t>NSE live market data</t>
+          <t>NSE live market data unavailable</t>
         </is>
       </c>
       <c r="E12" s="19" t="inlineStr">
         <is>
-          <t>2026-06-03 10:17:26</t>
+          <t>2026-06-05 02:02:19</t>
         </is>
       </c>
     </row>
@@ -3459,7 +3457,7 @@
     <row r="2">
       <c r="A2" s="21" t="inlineStr">
         <is>
-          <t>2026-06-03 10:18:15</t>
+          <t>2026-06-05 02:03:22</t>
         </is>
       </c>
       <c r="B2" s="21" t="inlineStr">
@@ -3491,7 +3489,7 @@
         <v>0</v>
       </c>
       <c r="J2" s="23" t="n">
-        <v>-6600</v>
+        <v>-9900</v>
       </c>
       <c r="K2" s="23" t="n">
         <v>1059300</v>
@@ -3506,7 +3504,7 @@
     <row r="3">
       <c r="A3" s="25" t="inlineStr">
         <is>
-          <t>2026-06-03 10:18:15</t>
+          <t>2026-06-05 02:03:22</t>
         </is>
       </c>
       <c r="B3" s="25" t="inlineStr">
@@ -3538,7 +3536,7 @@
         <v>0</v>
       </c>
       <c r="J3" s="27" t="n">
-        <v>18750</v>
+        <v>48750</v>
       </c>
       <c r="K3" s="27" t="n">
         <v>1113750</v>
@@ -3553,7 +3551,7 @@
     <row r="4">
       <c r="A4" s="21" t="inlineStr">
         <is>
-          <t>2026-06-03 10:18:15</t>
+          <t>2026-06-05 02:03:22</t>
         </is>
       </c>
       <c r="B4" s="21" t="inlineStr">
@@ -3600,7 +3598,7 @@
     <row r="5">
       <c r="A5" s="25" t="inlineStr">
         <is>
-          <t>2026-06-03 10:18:15</t>
+          <t>2026-06-05 02:03:22</t>
         </is>
       </c>
       <c r="B5" s="25" t="inlineStr">
@@ -3632,7 +3630,7 @@
         <v>0</v>
       </c>
       <c r="J5" s="27" t="n">
-        <v>10980</v>
+        <v>21960</v>
       </c>
       <c r="K5" s="27" t="n">
         <v>1277340</v>
@@ -3647,7 +3645,7 @@
     <row r="6">
       <c r="A6" s="21" t="inlineStr">
         <is>
-          <t>2026-06-03 10:18:15</t>
+          <t>2026-06-05 02:03:22</t>
         </is>
       </c>
       <c r="B6" s="21" t="inlineStr">
@@ -3679,7 +3677,7 @@
         <v>0</v>
       </c>
       <c r="J6" s="23" t="n">
-        <v>76270.75</v>
+        <v>72256.5</v>
       </c>
       <c r="K6" s="23" t="n">
         <v>2452706.75</v>
@@ -3694,7 +3692,7 @@
     <row r="7">
       <c r="A7" s="25" t="inlineStr">
         <is>
-          <t>2026-06-03 10:18:15</t>
+          <t>2026-06-05 02:03:22</t>
         </is>
       </c>
       <c r="B7" s="25" t="inlineStr">
@@ -3726,7 +3724,7 @@
         <v>0</v>
       </c>
       <c r="J7" s="27" t="n">
-        <v>127359</v>
+        <v>174529</v>
       </c>
       <c r="K7" s="27" t="n">
         <v>1698120</v>
@@ -3741,7 +3739,7 @@
     <row r="8">
       <c r="A8" s="21" t="inlineStr">
         <is>
-          <t>2026-06-03 10:18:15</t>
+          <t>2026-06-05 02:03:22</t>
         </is>
       </c>
       <c r="B8" s="21" t="inlineStr">
@@ -3773,7 +3771,7 @@
         <v>0</v>
       </c>
       <c r="J8" s="23" t="n">
-        <v>1955.959999999963</v>
+        <v>0</v>
       </c>
       <c r="K8" s="23" t="n">
         <v>819547.2400000001</v>
@@ -3788,7 +3786,7 @@
     <row r="9">
       <c r="A9" s="25" t="inlineStr">
         <is>
-          <t>2026-06-03 10:18:15</t>
+          <t>2026-06-05 02:03:22</t>
         </is>
       </c>
       <c r="B9" s="25" t="inlineStr">
@@ -3820,7 +3818,7 @@
         <v>0</v>
       </c>
       <c r="J9" s="27" t="n">
-        <v>-39328.25</v>
+        <v>-24202</v>
       </c>
       <c r="K9" s="27" t="n">
         <v>777489.25</v>
@@ -3835,7 +3833,7 @@
     <row r="10">
       <c r="A10" s="21" t="inlineStr">
         <is>
-          <t>2026-06-03 10:18:15</t>
+          <t>2026-06-05 02:03:22</t>
         </is>
       </c>
       <c r="B10" s="21" t="inlineStr">
@@ -3882,7 +3880,7 @@
     <row r="11">
       <c r="A11" s="25" t="inlineStr">
         <is>
-          <t>2026-06-03 10:18:15</t>
+          <t>2026-06-05 02:03:22</t>
         </is>
       </c>
       <c r="B11" s="25" t="inlineStr">
@@ -3914,7 +3912,7 @@
         <v>0</v>
       </c>
       <c r="J11" s="27" t="n">
-        <v>59693.40000000014</v>
+        <v>32142.60000000009</v>
       </c>
       <c r="K11" s="27" t="n">
         <v>1409682.6</v>
@@ -3929,7 +3927,7 @@
     <row r="12">
       <c r="A12" s="21" t="inlineStr">
         <is>
-          <t>2026-06-03 10:18:15</t>
+          <t>2026-06-05 02:03:22</t>
         </is>
       </c>
       <c r="B12" s="21" t="inlineStr">
@@ -3961,7 +3959,7 @@
         <v>0</v>
       </c>
       <c r="J12" s="23" t="n">
-        <v>-256018.1000000001</v>
+        <v>60596</v>
       </c>
       <c r="K12" s="23" t="n">
         <v>1681539</v>
@@ -3976,7 +3974,7 @@
     <row r="13">
       <c r="A13" s="25" t="inlineStr">
         <is>
-          <t>2026-06-03 10:18:15</t>
+          <t>2026-06-05 02:03:22</t>
         </is>
       </c>
       <c r="B13" s="25" t="inlineStr">
@@ -4023,7 +4021,7 @@
     <row r="14">
       <c r="A14" s="21" t="inlineStr">
         <is>
-          <t>2026-06-03 10:18:15</t>
+          <t>2026-06-05 02:03:22</t>
         </is>
       </c>
       <c r="B14" s="21" t="inlineStr">
@@ -4070,7 +4068,7 @@
     <row r="15">
       <c r="A15" s="25" t="inlineStr">
         <is>
-          <t>2026-06-03 10:18:15</t>
+          <t>2026-06-05 02:03:22</t>
         </is>
       </c>
       <c r="B15" s="25" t="inlineStr">
@@ -4117,7 +4115,7 @@
     <row r="16">
       <c r="A16" s="21" t="inlineStr">
         <is>
-          <t>2026-06-03 10:18:15</t>
+          <t>2026-06-05 02:03:22</t>
         </is>
       </c>
       <c r="B16" s="21" t="inlineStr">
@@ -4225,10 +4223,10 @@
         <v>32.1</v>
       </c>
       <c r="E2" t="n">
-        <v>31.9</v>
+        <v>31.8</v>
       </c>
       <c r="F2" t="n">
-        <v>1052700</v>
+        <v>1049400</v>
       </c>
     </row>
     <row r="3">
@@ -4249,10 +4247,10 @@
         <v>74.25</v>
       </c>
       <c r="E3" t="n">
-        <v>75.5</v>
+        <v>77.5</v>
       </c>
       <c r="F3" t="n">
-        <v>1132500</v>
+        <v>1162500</v>
       </c>
     </row>
     <row r="4">
@@ -4297,10 +4295,10 @@
         <v>87.25</v>
       </c>
       <c r="E5" t="n">
-        <v>88</v>
+        <v>88.75</v>
       </c>
       <c r="F5" t="n">
-        <v>1288320</v>
+        <v>1299300</v>
       </c>
     </row>
     <row r="6">
@@ -4321,10 +4319,10 @@
         <v>30.55</v>
       </c>
       <c r="E6" t="n">
-        <v>31.5</v>
+        <v>31.45</v>
       </c>
       <c r="F6" t="n">
-        <v>2528977.5</v>
+        <v>2524963.25</v>
       </c>
     </row>
     <row r="7">
@@ -4345,10 +4343,10 @@
         <v>360</v>
       </c>
       <c r="E7" t="n">
-        <v>387</v>
+        <v>397</v>
       </c>
       <c r="F7" t="n">
-        <v>1825479</v>
+        <v>1872649</v>
       </c>
     </row>
     <row r="8">
@@ -4369,10 +4367,10 @@
         <v>4.19</v>
       </c>
       <c r="E8" t="n">
-        <v>4.2</v>
+        <v>4.19</v>
       </c>
       <c r="F8" t="n">
-        <v>821503.2000000001</v>
+        <v>819547.2400000001</v>
       </c>
     </row>
     <row r="9">
@@ -4393,10 +4391,10 @@
         <v>12.85</v>
       </c>
       <c r="E9" t="n">
-        <v>12.2</v>
+        <v>12.45</v>
       </c>
       <c r="F9" t="n">
-        <v>738161</v>
+        <v>753287.25</v>
       </c>
     </row>
     <row r="10">
@@ -4441,10 +4439,10 @@
         <v>15.35</v>
       </c>
       <c r="E11" t="n">
-        <v>16</v>
+        <v>15.7</v>
       </c>
       <c r="F11" t="n">
-        <v>1469376</v>
+        <v>1441825.2</v>
       </c>
     </row>
     <row r="12">
@@ -4465,10 +4463,10 @@
         <v>55.5</v>
       </c>
       <c r="E12" t="n">
-        <v>47.05</v>
+        <v>57.5</v>
       </c>
       <c r="F12" t="n">
-        <v>1425520.9</v>
+        <v>1742135</v>
       </c>
     </row>
     <row r="13">

--- a/reports/MyPortfolio_Tracker_Kenya_Dashboard_Output.xlsx
+++ b/reports/MyPortfolio_Tracker_Kenya_Dashboard_Output.xlsx
@@ -820,7 +820,7 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>26594408.94</v>
+        <v>26331600.9</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
@@ -869,10 +869,10 @@
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>1049400</v>
+        <v>1056000</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>3.945942180431854</v>
+        <v>4.010390420280144</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -882,10 +882,10 @@
         </is>
       </c>
       <c r="B11" s="10" t="n">
-        <v>1162500</v>
+        <v>1158750</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>4.371219539500697</v>
+        <v>4.400605965435243</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -898,7 +898,7 @@
         <v>1299375</v>
       </c>
       <c r="C12" s="8" t="n">
-        <v>4.885895388506424</v>
+        <v>4.934660087454082</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -908,10 +908,10 @@
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>1299300</v>
+        <v>1288320</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>4.885613374342586</v>
+        <v>4.892676312741775</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -921,10 +921,10 @@
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>2524963.25</v>
+        <v>2545034.5</v>
       </c>
       <c r="C14" s="8" t="n">
-        <v>9.494338662297791</v>
+        <v>9.665323842881122</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="B15" s="10" t="n">
-        <v>1872649</v>
+        <v>1886800</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>7.041513891979734</v>
+        <v>7.165534701689938</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="B16" s="7" t="n">
-        <v>819547.2400000001</v>
+        <v>821503.2000000001</v>
       </c>
       <c r="C16" s="8" t="n">
-        <v>3.081652394866123</v>
+        <v>3.119837654838526</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -960,10 +960,10 @@
         </is>
       </c>
       <c r="B17" s="10" t="n">
-        <v>753287.25</v>
+        <v>750262</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>2.832502319188599</v>
+        <v>2.849283652935815</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -976,7 +976,7 @@
         <v>907270</v>
       </c>
       <c r="C18" s="8" t="n">
-        <v>3.411506539013159</v>
+        <v>3.445555792242013</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -989,7 +989,7 @@
         <v>1441825.2</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>5.421535042395269</v>
+        <v>5.475645804733429</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -999,10 +999,10 @@
         </is>
       </c>
       <c r="B20" s="7" t="n">
-        <v>1742135</v>
+        <v>1454304</v>
       </c>
       <c r="C20" s="8" t="n">
-        <v>6.550756604256384</v>
+        <v>5.523036770620354</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -1015,7 +1015,7 @@
         <v>2559858</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>9.625549512212624</v>
+        <v>9.721619318633984</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -1028,7 +1028,7 @@
         <v>1112299</v>
       </c>
       <c r="C22" s="8" t="n">
-        <v>4.182454298982439</v>
+        <v>4.224198157279529</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -1041,7 +1041,7 @@
         <v>6050000</v>
       </c>
       <c r="C23" s="11" t="n">
-        <v>22.74914254965954</v>
+        <v>22.97619511618832</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -1054,7 +1054,7 @@
         <v>2000000</v>
       </c>
       <c r="C24" s="8" t="n">
-        <v>7.52037770236679</v>
+        <v>7.595436402045726</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1"/>
@@ -1078,7 +1078,7 @@
         </is>
       </c>
       <c r="B28" s="8" t="n">
-        <v>18.08867048278156</v>
+        <v>18.23833278591124</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -1088,7 +1088,7 @@
         </is>
       </c>
       <c r="B29" s="11" t="n">
-        <v>7.52037770236679</v>
+        <v>7.595436402045726</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -1098,7 +1098,7 @@
         </is>
       </c>
       <c r="B30" s="8" t="n">
-        <v>13.80800381119506</v>
+        <v>13.94581747591351</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -1108,7 +1108,7 @@
         </is>
       </c>
       <c r="B31" s="11" t="n">
-        <v>15.38379818566481</v>
+        <v>14.4442383675958</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="B32" s="8" t="n">
-        <v>22.74914254965954</v>
+        <v>22.97619511618832</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B33" s="11" t="n">
-        <v>12.95566860603445</v>
+        <v>13.13465600946428</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -1138,7 +1138,7 @@
         </is>
       </c>
       <c r="B34" s="8" t="n">
-        <v>9.494338662297791</v>
+        <v>9.665323842881122</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1"/>
@@ -1276,13 +1276,13 @@
         </is>
       </c>
       <c r="C48" s="8" t="n">
-        <v>7.041513891979734</v>
+        <v>7.165534701689938</v>
       </c>
       <c r="D48" s="8" t="n">
         <v>6.666666666666667</v>
       </c>
       <c r="E48" s="8" t="n">
-        <v>0.3748472253130668</v>
+        <v>0.4988680350232713</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1"/>
@@ -1339,13 +1339,13 @@
         </is>
       </c>
       <c r="D54" s="3" t="n">
-        <v>252</v>
+        <v>329</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>100044</v>
+        <v>131600</v>
       </c>
       <c r="G54" s="15" t="inlineStr">
         <is>
@@ -1370,13 +1370,13 @@
         </is>
       </c>
       <c r="D55" s="16" t="n">
-        <v>8008</v>
+        <v>10594</v>
       </c>
       <c r="E55" s="10" t="n">
-        <v>12.45</v>
+        <v>12.4</v>
       </c>
       <c r="F55" s="10" t="n">
-        <v>99699.59999999999</v>
+        <v>131365.6</v>
       </c>
       <c r="G55" s="17" t="inlineStr">
         <is>
@@ -1528,13 +1528,13 @@
         <v>32.1</v>
       </c>
       <c r="G2" s="23" t="n">
-        <v>31.8</v>
+        <v>32</v>
       </c>
       <c r="H2" s="19" t="n">
         <v>1059300</v>
       </c>
       <c r="I2" s="23" t="n">
-        <v>1049400</v>
+        <v>1056000</v>
       </c>
       <c r="J2" s="23" t="n">
         <v>66000</v>
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="L2" s="19" t="n">
-        <v>31.8</v>
+        <v>32</v>
       </c>
       <c r="M2" s="19" t="inlineStr">
         <is>
@@ -1554,14 +1554,14 @@
       </c>
       <c r="N2" s="19" t="inlineStr">
         <is>
-          <t>2026-06-05 02:02:19</t>
+          <t>2026-06-05 10:43:00</t>
         </is>
       </c>
       <c r="O2" s="24" t="n">
-        <v>3.945942180431854</v>
+        <v>4.010390420280144</v>
       </c>
       <c r="P2" s="24" t="n">
-        <v>-0.9345794392523387</v>
+        <v>-0.3115264797507832</v>
       </c>
     </row>
     <row r="3">
@@ -1588,13 +1588,13 @@
         <v>74.25</v>
       </c>
       <c r="G3" s="27" t="n">
-        <v>77.5</v>
+        <v>77.25</v>
       </c>
       <c r="H3" s="17" t="n">
         <v>1113750</v>
       </c>
       <c r="I3" s="27" t="n">
-        <v>1162500</v>
+        <v>1158750</v>
       </c>
       <c r="J3" s="27" t="n">
         <v>30000</v>
@@ -1605,7 +1605,7 @@
         </is>
       </c>
       <c r="L3" s="17" t="n">
-        <v>77.5</v>
+        <v>77.25</v>
       </c>
       <c r="M3" s="17" t="inlineStr">
         <is>
@@ -1614,14 +1614,14 @@
       </c>
       <c r="N3" s="17" t="inlineStr">
         <is>
-          <t>2026-06-05 02:02:19</t>
+          <t>2026-06-05 10:43:00</t>
         </is>
       </c>
       <c r="O3" s="28" t="n">
-        <v>4.371219539500697</v>
+        <v>4.400605965435243</v>
       </c>
       <c r="P3" s="28" t="n">
-        <v>4.377104377104377</v>
+        <v>4.040404040404041</v>
       </c>
     </row>
     <row r="4">
@@ -1672,11 +1672,11 @@
       </c>
       <c r="N4" s="19" t="inlineStr">
         <is>
-          <t>2026-06-05 02:02:19</t>
+          <t>2026-06-05 10:43:00</t>
         </is>
       </c>
       <c r="O4" s="24" t="n">
-        <v>4.885895388506424</v>
+        <v>4.934660087454082</v>
       </c>
       <c r="P4" s="24" t="n">
         <v>2.99625468164794</v>
@@ -1706,13 +1706,13 @@
         <v>87.25</v>
       </c>
       <c r="G5" s="27" t="n">
-        <v>88.75</v>
+        <v>88</v>
       </c>
       <c r="H5" s="17" t="n">
         <v>1277340</v>
       </c>
       <c r="I5" s="27" t="n">
-        <v>1299300</v>
+        <v>1288320</v>
       </c>
       <c r="J5" s="27" t="n">
         <v>29280</v>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="L5" s="17" t="n">
-        <v>88.75</v>
+        <v>88</v>
       </c>
       <c r="M5" s="17" t="inlineStr">
         <is>
@@ -1732,14 +1732,14 @@
       </c>
       <c r="N5" s="17" t="inlineStr">
         <is>
-          <t>2026-06-05 02:02:19</t>
+          <t>2026-06-05 10:43:00</t>
         </is>
       </c>
       <c r="O5" s="28" t="n">
-        <v>4.885613374342586</v>
+        <v>4.892676312741775</v>
       </c>
       <c r="P5" s="28" t="n">
-        <v>1.71919770773639</v>
+        <v>0.8595988538681949</v>
       </c>
     </row>
     <row r="6">
@@ -1766,13 +1766,13 @@
         <v>30.55</v>
       </c>
       <c r="G6" s="23" t="n">
-        <v>31.45</v>
+        <v>31.7</v>
       </c>
       <c r="H6" s="19" t="n">
         <v>2452706.75</v>
       </c>
       <c r="I6" s="23" t="n">
-        <v>2524963.25</v>
+        <v>2545034.5</v>
       </c>
       <c r="J6" s="23" t="n">
         <v>160570</v>
@@ -1783,7 +1783,7 @@
         </is>
       </c>
       <c r="L6" s="19" t="n">
-        <v>31.45</v>
+        <v>31.7</v>
       </c>
       <c r="M6" s="19" t="inlineStr">
         <is>
@@ -1792,14 +1792,14 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>2026-06-05 02:02:19</t>
+          <t>2026-06-05 10:43:00</t>
         </is>
       </c>
       <c r="O6" s="24" t="n">
-        <v>9.494338662297791</v>
+        <v>9.665323842881122</v>
       </c>
       <c r="P6" s="24" t="n">
-        <v>2.945990180032728</v>
+        <v>3.764320785597377</v>
       </c>
     </row>
     <row r="7">
@@ -1826,13 +1826,13 @@
         <v>360</v>
       </c>
       <c r="G7" s="27" t="n">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="H7" s="17" t="n">
         <v>1698120</v>
       </c>
       <c r="I7" s="27" t="n">
-        <v>1872649</v>
+        <v>1886800</v>
       </c>
       <c r="J7" s="27" t="n">
         <v>9434</v>
@@ -1843,7 +1843,7 @@
         </is>
       </c>
       <c r="L7" s="17" t="n">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="M7" s="17" t="inlineStr">
         <is>
@@ -1852,14 +1852,14 @@
       </c>
       <c r="N7" s="17" t="inlineStr">
         <is>
-          <t>2026-06-05 02:02:19</t>
+          <t>2026-06-05 10:43:00</t>
         </is>
       </c>
       <c r="O7" s="28" t="n">
-        <v>7.041513891979734</v>
+        <v>7.165534701689938</v>
       </c>
       <c r="P7" s="28" t="n">
-        <v>10.27777777777778</v>
+        <v>11.11111111111111</v>
       </c>
     </row>
     <row r="8">
@@ -1886,13 +1886,13 @@
         <v>4.19</v>
       </c>
       <c r="G8" s="23" t="n">
-        <v>4.19</v>
+        <v>4.2</v>
       </c>
       <c r="H8" s="19" t="n">
         <v>819547.2400000001</v>
       </c>
       <c r="I8" s="23" t="n">
-        <v>819547.2400000001</v>
+        <v>821503.2000000001</v>
       </c>
       <c r="J8" s="23" t="n">
         <v>391191.9999999999</v>
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="L8" s="19" t="n">
-        <v>4.19</v>
+        <v>4.2</v>
       </c>
       <c r="M8" s="19" t="inlineStr">
         <is>
@@ -1912,14 +1912,14 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>2026-06-05 02:02:19</t>
+          <t>2026-06-05 10:43:00</t>
         </is>
       </c>
       <c r="O8" s="24" t="n">
-        <v>3.081652394866123</v>
+        <v>3.119837654838526</v>
       </c>
       <c r="P8" s="24" t="n">
-        <v>0</v>
+        <v>0.2386634844868684</v>
       </c>
     </row>
     <row r="9">
@@ -1946,13 +1946,13 @@
         <v>12.85</v>
       </c>
       <c r="G9" s="27" t="n">
-        <v>12.45</v>
+        <v>12.4</v>
       </c>
       <c r="H9" s="17" t="n">
         <v>777489.25</v>
       </c>
       <c r="I9" s="27" t="n">
-        <v>753287.25</v>
+        <v>750262</v>
       </c>
       <c r="J9" s="27" t="n">
         <v>121010</v>
@@ -1963,7 +1963,7 @@
         </is>
       </c>
       <c r="L9" s="17" t="n">
-        <v>12.45</v>
+        <v>12.4</v>
       </c>
       <c r="M9" s="17" t="inlineStr">
         <is>
@@ -1972,14 +1972,14 @@
       </c>
       <c r="N9" s="17" t="inlineStr">
         <is>
-          <t>2026-06-05 02:02:19</t>
+          <t>2026-06-05 10:43:00</t>
         </is>
       </c>
       <c r="O9" s="28" t="n">
-        <v>2.832502319188599</v>
+        <v>2.849283652935815</v>
       </c>
       <c r="P9" s="28" t="n">
-        <v>-3.112840466926073</v>
+        <v>-3.501945525291823</v>
       </c>
     </row>
     <row r="10">
@@ -2032,11 +2032,11 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>2026-06-05 02:02:19</t>
+          <t>2026-06-05 10:43:00</t>
         </is>
       </c>
       <c r="O10" s="24" t="n">
-        <v>3.411506539013159</v>
+        <v>3.445555792242013</v>
       </c>
       <c r="P10" s="24" t="n">
         <v>-0.8714596949891076</v>
@@ -2092,11 +2092,11 @@
       </c>
       <c r="N11" s="17" t="inlineStr">
         <is>
-          <t>2026-06-05 02:02:19</t>
+          <t>2026-06-05 10:43:00</t>
         </is>
       </c>
       <c r="O11" s="28" t="n">
-        <v>5.421535042395269</v>
+        <v>5.475645804733429</v>
       </c>
       <c r="P11" s="28" t="n">
         <v>2.280130293159607</v>
@@ -2126,13 +2126,13 @@
         <v>55.5</v>
       </c>
       <c r="G12" s="23" t="n">
-        <v>57.5</v>
+        <v>48</v>
       </c>
       <c r="H12" s="19" t="n">
         <v>1681539</v>
       </c>
       <c r="I12" s="23" t="n">
-        <v>1742135</v>
+        <v>1454304</v>
       </c>
       <c r="J12" s="23" t="n">
         <v>60596</v>
@@ -2142,22 +2142,24 @@
           <t>TOTL</t>
         </is>
       </c>
-      <c r="L12" s="19" t="inlineStr"/>
+      <c r="L12" s="19" t="n">
+        <v>48</v>
+      </c>
       <c r="M12" s="19" t="inlineStr">
         <is>
-          <t>NSE live market data unavailable</t>
+          <t>NSE live market data</t>
         </is>
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>2026-06-05 02:02:19</t>
+          <t>2026-06-05 10:43:00</t>
         </is>
       </c>
       <c r="O12" s="24" t="n">
-        <v>6.550756604256384</v>
+        <v>5.523036770620354</v>
       </c>
       <c r="P12" s="24" t="n">
-        <v>3.603603603603604</v>
+        <v>-13.51351351351351</v>
       </c>
     </row>
     <row r="13">
@@ -2204,7 +2206,7 @@
       </c>
       <c r="N13" s="17" t="inlineStr"/>
       <c r="O13" s="28" t="n">
-        <v>9.625549512212624</v>
+        <v>9.721619318633984</v>
       </c>
       <c r="P13" s="28" t="n">
         <v>0.003828483920367535</v>
@@ -2254,7 +2256,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr"/>
       <c r="O14" s="24" t="n">
-        <v>4.182454298982439</v>
+        <v>4.224198157279529</v>
       </c>
       <c r="P14" s="24" t="n">
         <v>0.01744439598778892</v>
@@ -2304,7 +2306,7 @@
       </c>
       <c r="N15" s="17" t="inlineStr"/>
       <c r="O15" s="28" t="n">
-        <v>22.74914254965954</v>
+        <v>22.97619511618832</v>
       </c>
       <c r="P15" s="28" t="n">
         <v>0</v>
@@ -2354,7 +2356,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr"/>
       <c r="O16" s="24" t="n">
-        <v>7.52037770236679</v>
+        <v>7.595436402045726</v>
       </c>
       <c r="P16" s="24" t="n">
         <v>0</v>
@@ -2441,7 +2443,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="23" t="n">
-        <v>1049400</v>
+        <v>1056000</v>
       </c>
       <c r="H2" s="19" t="n">
         <v>0</v>
@@ -2463,7 +2465,7 @@
         <v>0</v>
       </c>
       <c r="G3" s="27" t="n">
-        <v>1162500</v>
+        <v>1158750</v>
       </c>
       <c r="H3" s="17" t="n">
         <v>0</v>
@@ -2507,7 +2509,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="27" t="n">
-        <v>1299300</v>
+        <v>1288320</v>
       </c>
       <c r="H5" s="17" t="n">
         <v>0</v>
@@ -2529,7 +2531,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="23" t="n">
-        <v>2524963.25</v>
+        <v>2545034.5</v>
       </c>
       <c r="H6" s="19" t="n">
         <v>0</v>
@@ -2551,7 +2553,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="27" t="n">
-        <v>1872649</v>
+        <v>1886800</v>
       </c>
       <c r="H7" s="17" t="n">
         <v>0</v>
@@ -2573,7 +2575,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="23" t="n">
-        <v>819547.2400000001</v>
+        <v>821503.2000000001</v>
       </c>
       <c r="H8" s="19" t="n">
         <v>0</v>
@@ -2595,7 +2597,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="27" t="n">
-        <v>753287.25</v>
+        <v>750262</v>
       </c>
       <c r="H9" s="17" t="n">
         <v>0</v>
@@ -2659,7 +2661,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="23" t="n">
-        <v>1742135</v>
+        <v>1454304</v>
       </c>
       <c r="H12" s="19" t="n">
         <v>0</v>
@@ -2828,7 +2830,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>26594408.94</v>
+        <v>26331600.9</v>
       </c>
       <c r="C2" s="23" t="inlineStr">
         <is>
@@ -3027,7 +3029,7 @@
         </is>
       </c>
       <c r="C2" s="23" t="n">
-        <v>31.8</v>
+        <v>32</v>
       </c>
       <c r="D2" s="19" t="inlineStr">
         <is>
@@ -3036,7 +3038,7 @@
       </c>
       <c r="E2" s="19" t="inlineStr">
         <is>
-          <t>2026-06-05 02:02:19</t>
+          <t>2026-06-05 10:43:00</t>
         </is>
       </c>
     </row>
@@ -3052,7 +3054,7 @@
         </is>
       </c>
       <c r="C3" s="27" t="n">
-        <v>77.5</v>
+        <v>77.25</v>
       </c>
       <c r="D3" s="17" t="inlineStr">
         <is>
@@ -3061,7 +3063,7 @@
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>2026-06-05 02:02:19</t>
+          <t>2026-06-05 10:43:00</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3088,7 @@
       </c>
       <c r="E4" s="19" t="inlineStr">
         <is>
-          <t>2026-06-05 02:02:19</t>
+          <t>2026-06-05 10:43:00</t>
         </is>
       </c>
     </row>
@@ -3102,7 +3104,7 @@
         </is>
       </c>
       <c r="C5" s="27" t="n">
-        <v>88.75</v>
+        <v>88</v>
       </c>
       <c r="D5" s="17" t="inlineStr">
         <is>
@@ -3111,7 +3113,7 @@
       </c>
       <c r="E5" s="17" t="inlineStr">
         <is>
-          <t>2026-06-05 02:02:19</t>
+          <t>2026-06-05 10:43:00</t>
         </is>
       </c>
     </row>
@@ -3127,7 +3129,7 @@
         </is>
       </c>
       <c r="C6" s="23" t="n">
-        <v>31.45</v>
+        <v>31.7</v>
       </c>
       <c r="D6" s="19" t="inlineStr">
         <is>
@@ -3136,7 +3138,7 @@
       </c>
       <c r="E6" s="19" t="inlineStr">
         <is>
-          <t>2026-06-05 02:02:19</t>
+          <t>2026-06-05 10:43:00</t>
         </is>
       </c>
     </row>
@@ -3152,7 +3154,7 @@
         </is>
       </c>
       <c r="C7" s="27" t="n">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="D7" s="17" t="inlineStr">
         <is>
@@ -3161,7 +3163,7 @@
       </c>
       <c r="E7" s="17" t="inlineStr">
         <is>
-          <t>2026-06-05 02:02:19</t>
+          <t>2026-06-05 10:43:00</t>
         </is>
       </c>
     </row>
@@ -3177,7 +3179,7 @@
         </is>
       </c>
       <c r="C8" s="23" t="n">
-        <v>4.19</v>
+        <v>4.2</v>
       </c>
       <c r="D8" s="19" t="inlineStr">
         <is>
@@ -3186,7 +3188,7 @@
       </c>
       <c r="E8" s="19" t="inlineStr">
         <is>
-          <t>2026-06-05 02:02:19</t>
+          <t>2026-06-05 10:43:00</t>
         </is>
       </c>
     </row>
@@ -3202,7 +3204,7 @@
         </is>
       </c>
       <c r="C9" s="27" t="n">
-        <v>12.45</v>
+        <v>12.4</v>
       </c>
       <c r="D9" s="17" t="inlineStr">
         <is>
@@ -3211,7 +3213,7 @@
       </c>
       <c r="E9" s="17" t="inlineStr">
         <is>
-          <t>2026-06-05 02:02:19</t>
+          <t>2026-06-05 10:43:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3238,7 @@
       </c>
       <c r="E10" s="19" t="inlineStr">
         <is>
-          <t>2026-06-05 02:02:19</t>
+          <t>2026-06-05 10:43:00</t>
         </is>
       </c>
     </row>
@@ -3261,7 +3263,7 @@
       </c>
       <c r="E11" s="17" t="inlineStr">
         <is>
-          <t>2026-06-05 02:02:19</t>
+          <t>2026-06-05 10:43:00</t>
         </is>
       </c>
     </row>
@@ -3277,16 +3279,16 @@
         </is>
       </c>
       <c r="C12" s="23" t="n">
-        <v>57.5</v>
+        <v>48</v>
       </c>
       <c r="D12" s="19" t="inlineStr">
         <is>
-          <t>NSE live market data unavailable</t>
+          <t>NSE live market data</t>
         </is>
       </c>
       <c r="E12" s="19" t="inlineStr">
         <is>
-          <t>2026-06-05 02:02:19</t>
+          <t>2026-06-05 10:43:00</t>
         </is>
       </c>
     </row>
@@ -3457,7 +3459,7 @@
     <row r="2">
       <c r="A2" s="21" t="inlineStr">
         <is>
-          <t>2026-06-05 02:03:22</t>
+          <t>2026-06-05 10:43:55</t>
         </is>
       </c>
       <c r="B2" s="21" t="inlineStr">
@@ -3489,7 +3491,7 @@
         <v>0</v>
       </c>
       <c r="J2" s="23" t="n">
-        <v>-9900</v>
+        <v>-3300</v>
       </c>
       <c r="K2" s="23" t="n">
         <v>1059300</v>
@@ -3504,7 +3506,7 @@
     <row r="3">
       <c r="A3" s="25" t="inlineStr">
         <is>
-          <t>2026-06-05 02:03:22</t>
+          <t>2026-06-05 10:43:55</t>
         </is>
       </c>
       <c r="B3" s="25" t="inlineStr">
@@ -3536,7 +3538,7 @@
         <v>0</v>
       </c>
       <c r="J3" s="27" t="n">
-        <v>48750</v>
+        <v>45000</v>
       </c>
       <c r="K3" s="27" t="n">
         <v>1113750</v>
@@ -3551,7 +3553,7 @@
     <row r="4">
       <c r="A4" s="21" t="inlineStr">
         <is>
-          <t>2026-06-05 02:03:22</t>
+          <t>2026-06-05 10:43:55</t>
         </is>
       </c>
       <c r="B4" s="21" t="inlineStr">
@@ -3598,7 +3600,7 @@
     <row r="5">
       <c r="A5" s="25" t="inlineStr">
         <is>
-          <t>2026-06-05 02:03:22</t>
+          <t>2026-06-05 10:43:55</t>
         </is>
       </c>
       <c r="B5" s="25" t="inlineStr">
@@ -3630,7 +3632,7 @@
         <v>0</v>
       </c>
       <c r="J5" s="27" t="n">
-        <v>21960</v>
+        <v>10980</v>
       </c>
       <c r="K5" s="27" t="n">
         <v>1277340</v>
@@ -3645,7 +3647,7 @@
     <row r="6">
       <c r="A6" s="21" t="inlineStr">
         <is>
-          <t>2026-06-05 02:03:22</t>
+          <t>2026-06-05 10:43:55</t>
         </is>
       </c>
       <c r="B6" s="21" t="inlineStr">
@@ -3677,7 +3679,7 @@
         <v>0</v>
       </c>
       <c r="J6" s="23" t="n">
-        <v>72256.5</v>
+        <v>92327.75</v>
       </c>
       <c r="K6" s="23" t="n">
         <v>2452706.75</v>
@@ -3692,7 +3694,7 @@
     <row r="7">
       <c r="A7" s="25" t="inlineStr">
         <is>
-          <t>2026-06-05 02:03:22</t>
+          <t>2026-06-05 10:43:55</t>
         </is>
       </c>
       <c r="B7" s="25" t="inlineStr">
@@ -3724,7 +3726,7 @@
         <v>0</v>
       </c>
       <c r="J7" s="27" t="n">
-        <v>174529</v>
+        <v>188680</v>
       </c>
       <c r="K7" s="27" t="n">
         <v>1698120</v>
@@ -3739,7 +3741,7 @@
     <row r="8">
       <c r="A8" s="21" t="inlineStr">
         <is>
-          <t>2026-06-05 02:03:22</t>
+          <t>2026-06-05 10:43:55</t>
         </is>
       </c>
       <c r="B8" s="21" t="inlineStr">
@@ -3771,7 +3773,7 @@
         <v>0</v>
       </c>
       <c r="J8" s="23" t="n">
-        <v>0</v>
+        <v>1955.959999999963</v>
       </c>
       <c r="K8" s="23" t="n">
         <v>819547.2400000001</v>
@@ -3786,7 +3788,7 @@
     <row r="9">
       <c r="A9" s="25" t="inlineStr">
         <is>
-          <t>2026-06-05 02:03:22</t>
+          <t>2026-06-05 10:43:55</t>
         </is>
       </c>
       <c r="B9" s="25" t="inlineStr">
@@ -3818,7 +3820,7 @@
         <v>0</v>
       </c>
       <c r="J9" s="27" t="n">
-        <v>-24202</v>
+        <v>-27227.25</v>
       </c>
       <c r="K9" s="27" t="n">
         <v>777489.25</v>
@@ -3833,7 +3835,7 @@
     <row r="10">
       <c r="A10" s="21" t="inlineStr">
         <is>
-          <t>2026-06-05 02:03:22</t>
+          <t>2026-06-05 10:43:55</t>
         </is>
       </c>
       <c r="B10" s="21" t="inlineStr">
@@ -3880,7 +3882,7 @@
     <row r="11">
       <c r="A11" s="25" t="inlineStr">
         <is>
-          <t>2026-06-05 02:03:22</t>
+          <t>2026-06-05 10:43:55</t>
         </is>
       </c>
       <c r="B11" s="25" t="inlineStr">
@@ -3927,7 +3929,7 @@
     <row r="12">
       <c r="A12" s="21" t="inlineStr">
         <is>
-          <t>2026-06-05 02:03:22</t>
+          <t>2026-06-05 10:43:55</t>
         </is>
       </c>
       <c r="B12" s="21" t="inlineStr">
@@ -3959,7 +3961,7 @@
         <v>0</v>
       </c>
       <c r="J12" s="23" t="n">
-        <v>60596</v>
+        <v>-227235</v>
       </c>
       <c r="K12" s="23" t="n">
         <v>1681539</v>
@@ -3974,7 +3976,7 @@
     <row r="13">
       <c r="A13" s="25" t="inlineStr">
         <is>
-          <t>2026-06-05 02:03:22</t>
+          <t>2026-06-05 10:43:55</t>
         </is>
       </c>
       <c r="B13" s="25" t="inlineStr">
@@ -4021,7 +4023,7 @@
     <row r="14">
       <c r="A14" s="21" t="inlineStr">
         <is>
-          <t>2026-06-05 02:03:22</t>
+          <t>2026-06-05 10:43:55</t>
         </is>
       </c>
       <c r="B14" s="21" t="inlineStr">
@@ -4068,7 +4070,7 @@
     <row r="15">
       <c r="A15" s="25" t="inlineStr">
         <is>
-          <t>2026-06-05 02:03:22</t>
+          <t>2026-06-05 10:43:55</t>
         </is>
       </c>
       <c r="B15" s="25" t="inlineStr">
@@ -4115,7 +4117,7 @@
     <row r="16">
       <c r="A16" s="21" t="inlineStr">
         <is>
-          <t>2026-06-05 02:03:22</t>
+          <t>2026-06-05 10:43:55</t>
         </is>
       </c>
       <c r="B16" s="21" t="inlineStr">
@@ -4223,10 +4225,10 @@
         <v>32.1</v>
       </c>
       <c r="E2" t="n">
-        <v>31.8</v>
+        <v>32</v>
       </c>
       <c r="F2" t="n">
-        <v>1049400</v>
+        <v>1056000</v>
       </c>
     </row>
     <row r="3">
@@ -4247,10 +4249,10 @@
         <v>74.25</v>
       </c>
       <c r="E3" t="n">
-        <v>77.5</v>
+        <v>77.25</v>
       </c>
       <c r="F3" t="n">
-        <v>1162500</v>
+        <v>1158750</v>
       </c>
     </row>
     <row r="4">
@@ -4295,10 +4297,10 @@
         <v>87.25</v>
       </c>
       <c r="E5" t="n">
-        <v>88.75</v>
+        <v>88</v>
       </c>
       <c r="F5" t="n">
-        <v>1299300</v>
+        <v>1288320</v>
       </c>
     </row>
     <row r="6">
@@ -4319,10 +4321,10 @@
         <v>30.55</v>
       </c>
       <c r="E6" t="n">
-        <v>31.45</v>
+        <v>31.7</v>
       </c>
       <c r="F6" t="n">
-        <v>2524963.25</v>
+        <v>2545034.5</v>
       </c>
     </row>
     <row r="7">
@@ -4343,10 +4345,10 @@
         <v>360</v>
       </c>
       <c r="E7" t="n">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="F7" t="n">
-        <v>1872649</v>
+        <v>1886800</v>
       </c>
     </row>
     <row r="8">
@@ -4367,10 +4369,10 @@
         <v>4.19</v>
       </c>
       <c r="E8" t="n">
-        <v>4.19</v>
+        <v>4.2</v>
       </c>
       <c r="F8" t="n">
-        <v>819547.2400000001</v>
+        <v>821503.2000000001</v>
       </c>
     </row>
     <row r="9">
@@ -4391,10 +4393,10 @@
         <v>12.85</v>
       </c>
       <c r="E9" t="n">
-        <v>12.45</v>
+        <v>12.4</v>
       </c>
       <c r="F9" t="n">
-        <v>753287.25</v>
+        <v>750262</v>
       </c>
     </row>
     <row r="10">
@@ -4463,10 +4465,10 @@
         <v>55.5</v>
       </c>
       <c r="E12" t="n">
-        <v>57.5</v>
+        <v>48</v>
       </c>
       <c r="F12" t="n">
-        <v>1742135</v>
+        <v>1454304</v>
       </c>
     </row>
     <row r="13">
